--- a/Output/Chandrashekhar Bawankule/extracted_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A269"/>
+  <dimension ref="A1:A289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,1876 +438,2016 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178088/</t>
+          <t>https://mahasamvad.in/179502/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/rohit-pawar-should-prove-the-allegations-otherwise-he-should-retire-from-politics-revenue-minister-chandrashekhar-bawankules-counterattack-a-a876-c1000/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/land-approved-for-bhandara-judges-residence-revenue-minister-chandrashekhar-bawankules-initiative.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/gunaratna-sadavarte-meets-revenue-minister-chandrashekhar-bawankule-terms-jaranges-gr-as-unconstitutional-in-obc-vs-maratha-quota-debate-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/bjp-ministry-chandrashekhar-bawankule-target-mla-rohit-pawar-over-company-fine-waived-983204.html</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418/amp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/special-campaign-from-17th-to-22nd-september-to-accelerate-baliraja-shet-panand-road-scheme-revenue-minister-chandrashekhar-bawankule/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-plans-law-to-lease-tribal-barren-land-to-private-companies</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AF-%E0%A4%97-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%9D%E0%A4%97%E0%A4%A1-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MeEni</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AF-%E0%A4%97-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%9D%E0%A4%97%E0%A4%A1-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MeEni?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-rohit-pawar-target-chandra-shekhar-bawankule-revenue-department-megha-engineering-discount-dumper-return-135876572.html</t>
+          <t>https://mahasamvad.in/179430/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178012/</t>
+          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-video-vsd-99-5388756/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://chandablast.com/?p=50394</t>
+          <t>https://chandablast.com/?p=50932</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/mumbai/obc-leaders-chhagan-bhujbal-reservation-maharashtra-pankaja-munde</t>
+          <t>https://deshdoot.com/malegaon-revenue-minister-chandrashekhar-bawankule-grampanchayats-land/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/twitter-war-breaks-out-between-rohit-pawar-and-chandrashekhar-bawankule-over-megha-engineering/920492/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/21/maharashtra-knows-what-lights-vadettiwar-lit-when-he-was-a-minister-minister-chandrashekhar-bawankule-criticiz.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/resolve-the-sand-issue-in-konkan-within-three-months/</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nilesh-rane-demands-separate-sand-policy-for-traders-in-konkan-review-meeting-sp96</t>
+          <t>https://mahasamvad.in/178572/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/rohit-pawar-megha-engineering-penalty-waiver-chandrashekhar-bawankule-political-controversy-rm82</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B9-%E0%A4%B2%E0%A4%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A4%9A-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%96-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1yazrQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/politics/rohit-pawar-challenge-accepted-twitter-proof-devabhau-advertisment/</t>
+          <t>https://www.loksatta.com/nagpur/revenue-minister-bawankules-announcement-in-gadchiroli-phm-00-5385317/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/10/?m=0</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-tribal-farmers-land-leasing-income-boost</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/gunratna-sadavarte-challenges-mahayuti-government-and-radhakrishna-vikhe-patil-over-withdraw-cases-against-maratha-protesters-as11</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439/amp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/campaign-unveiled-to-boost-baliraja-farmroad-initiativeset-to-minimize-future-conflicts</t>
+          <t>https://www.lokmat.com/agriculture/farming-ideas/revenue-ministers-big-announcement-on-the-excavation-of-murum-for-the-repair-of-panand-roads-in-the-state-a-a975/amp/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-launches-chief-minister-baliraja-panand-road-scheme-125091000009_1.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/rohit-pawar-on-bawankule-rohit-pawar-again-targeted-revenue-minister-chandrashekhar-bawankule-said-the-suspension-of-engineering-fine-is-a-fine/131885/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852/amp</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/chandrasekhar-bawankule-and-ncps-rohit-pawar-questioned-eachother/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/rohit-pawar-challenges-chandrashekhar-bawankule-over-megha-engineering-fine-waiver-marathi-news-036967.html</t>
+          <t>https://mpbreakingnews.in/marathi/politics/new-districts-in-maharashtra-chandrashekhar-bawankule-big-statement-03-698118</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/chandrasekhar-bawankule-said-there-will-be-no-injustice-to-obcs/</t>
+          <t>https://deshonnati.com/officials-should-act-without-condoning-any-wrongdoing/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/rohit-pawar-rohit-pawar-made-serious-allegations-against-revenue-minister-chandrashekhar-bawankule-said-i-without-evidence/131714/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/review-of-the-work-of-konkan-revenue-department-chandrashekhar-bawankule-directs-that-the-revenue-system-should-utilize-its-capabilities/132124/</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece/amp/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/politics/prove-the-allegations-or-else-retire-from-politics-chandrashekhar-bawankules-direct-challenge-to-rohit-pawar/131706/</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3634952-controversy-brews-over-garba-entry-restrictions-amidst-navratri-celebrations?amp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/vidarbha/216208/</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/dont-create-obc-vs-maratha-divide-in-society-says-chandrashekhar-bawankule/article70034519.ece</t>
+          <t>https://www.ptinews.com/editor-detail/Tribals-in-Maharashtra-can-now-lease-barren-land-to-private-entities;-govt-to-bring-law-Minister/2932964</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1292529</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/rohit-pawar-vs-bjp-minister-chandrashekhar-bawankule-fine-waiver-to-megha-engineering-2785965-2025-09-11</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/current-affairs/munde-assures-obcs-will-not-be-sidelined-amid-maratha-quota-row-1902874</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2-933cr-pending-funds/2920779</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-allocates-land-for-intelligence-bureau-residential-quarters-panvel-10239916/</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining?amp</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/entertainment/southcinema/bawankule-announces-kalamkari-garment-cluster-in-koradi/ar-AA1Mqj9x</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bes11-mh-bawankule-farmers.amp.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://thesouthfirst.com/news/nda-ruled-maharashtra-waived-off-fine-on-bjps-biggest-electoral-bond-donor-meil-says-mla/</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3622267-maharashtra-government-navigates-maratha-reservation-debate-amid-obc-concerns</t>
+          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bawankule-backs-organisers--rights--wadettiwar-slams-move/2932800</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-firmly-defend-maratha-and-obc-quotas-bawankule/articleshow/123752163.cms</t>
+          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bjp-minister-backs-organisers--rights--cong-slams-move/2934001</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/blanket-issuance-kunbi-status-marathas-not-acceptable-maharashtra-bawankule-10242237/</t>
+          <t>https://www.ptinews.com/story/national/No-opposition-to-Badgujar-s-induction-into-BJP-Fadnavis/2655228</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/other/megha-engineering-fined-rs-94-6-crore-for-illegal-mining-in-maharashtra-s-jalna/ar-AA1Iroje?ocid=finance-verthp-feeds&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers?amp</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/look-beyond-roads-focus-on-health-edu-development-in-villages-bawankule-to-zp/articleshow/123793225.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom22-mh-tribals-land-lease.amp.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/no-injustice-to-obcs-kunbi-certificates-to-be-issued-only-after-due-verification-bawankule/ar-AA1Mh8fw</t>
+          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/no-injustice-to-obcs-accept-only-verified-records-for-maratha-kunbi-certificate-bawankule/articleshow/123816212.cms</t>
+          <t>https://www.devdiscourse.com/article/law-order/3634600-maharashtras-new-lease-law-a-boon-or-bane-for-tribal-farmers?amp</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/clear-health-proposals-in-nagpur-amravati-melghat-bawankule/articleshow/123816301.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/bawankule-gave-firm-rs90cr-penalty-waiver-in-poll-bonds-favouritism-rohit/articleshow/123772937.cms</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-hits-back-at-oppn-targeting-cm-over-devabhau-advt/articleshow/123772690.cms</t>
+          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-announces-kalamkari-garment-cluster-in-koradi/articleshow/123853712.cms</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3622717-maharashtras-obc-reforms-securing-justice-amid-maratha-quota-debate</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-manoj-jarange-govt-at-odds-over-obc-certificates-for-marathas-23593384</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/maharashtra/good-news-for-farmers-chief-minister-baliraja-panand-roads-scheme-in-the-state-announcement-from-minister-chandrashekhar-bawankule</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bes11-mh-bawankule-farmers.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankule-hails-signing-of-agreement-for-new-nagpur-development-project/09081753</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/obc-communitys-concerns-over-reservation-will-not-be-ignored-minister-pankaja-munde/2901852</t>
+          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ncp-sps-rohit-pawar-maha-minister-chandrashekhar-bawankule-trade-barbs-over-alleged-waiver-of-90-crore-penalty-on-megha-engineering</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809-amp.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-revenue-minister-orders-people-centric-approach-to-resolve-konkan-land-issues</t>
+          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840-amp.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-expedited-healthcare-development-in-nagpur-amravati-under-minister-bawankules-guidance</t>
+          <t>https://www.msn.com/mr-in/news/other/chandrashekhar-bawankule-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B9-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9C%E0%A4%96%E0%A4%AE%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%AE-%E0%A4%A0-%E0%A4%9A-%E0%A4%B3%E0%A5%82-%E0%A4%A8%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A4%A4-%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A4%E0%A4%B0%E0%A5%8D%E0%A4%AB%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%AE-%E0%A4%AE-%E0%A4%97%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1Cn5Cg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-launches-farm-access-roads-scheme-to-boost-agriculture-and-farmers-welfare</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/stormy-obc-sub-cabinet-committee-meeting-chhagan-bhujbal-slams-grs-demands-fair-share-of-funds</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/no-injustice-to-obcs-kunbi-certificates-to-be-issued-only-after-due-verification-bawankule/ar-AA1Mh8fw?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/no-injustice-to-obcs-kunbi-certificates-to-be-issued-only-after-due-verification-bawankule/2902881</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/amp_articleshow/123887314.cms</t>
+          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-manoj-jarange-govt-at-odds-over-obc-certificates-for-marathas-23593384</t>
+          <t>https://www.esakal.com/pune/chandrashekhar-bawankule-slams-uddhav-thackeray-says-opposing-reservation-is-wrong-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/obc-caste-certificate-should-not-be-issued-without-proof-chandrashekhar-bawankule-press-conference-after-the-obc-sub-committee-meeting-mumbai-maharashtra-news-mhs25091004064</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/bjp-targets-51-percent-in-local-bodies-election-said-chandrashekhar-bawankule-a-a382-c719/</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-orders-sangli-wind-energy-land-probe-ocd-94-5366638/</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/177929/</t>
+          <t>https://mahasamvad.in/178575/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/there-will-be-no-injustice-to-obcs-no-false-records-important-decision-taken-in-the-cabinet-sub-committee-meet.html</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maratha-arakashan-%E0%A4%B9%E0%A5%88%E0%A4%A6%E0%A4%B0-%E0%A4%AC-%E0%A4%A6-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F-%E0%A4%AF%E0%A4%B0%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A6%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1LXgLq</t>
+          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/amravati-health-infrastructure-to-see-major-boost-minister-chandrashekhar-bawankules-urgent-directions-vsb99</t>
+          <t>https://www.lokmat.com/nagpur/chandrasekhar-bavankule-bhandara-districts-guardian-minister/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/nagpur/chandrasekhar-bavankule-bhandara-districts-guardian-minister/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/chandrashekhar-bawankule-will-discuss-with-chhagan-bhujbal-in-meeting-regarding-obc-community-demands/videoshow/123779234.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/chandrasekhar-bawankule-you-cannot-get-caste-certificate-with-sword-at-officers-throat-283530/</t>
+          <t>https://www.lokmat.com/nagpur/cctvs-gardens-and-sports-grounds-instruction-chandrasekhar-bavankules-interaction/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/nagpur/cctvs-gardens-and-sports-grounds-instruction-chandrasekhar-bavankules-interaction/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/rohit-pawar-chandrashekhar-bawankule-dispute-mega-engineering-fine-135880348.html</t>
+          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/bjp-targets-51-percent-in-local-bodies-election-said-chandrashekhar-bawankule-a-a382-c719/?utm_source=Lokmat.com&amp;utm_medium=shorts_mobile_headline</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/177925/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/chandrashekhar-bawankule/</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/due-to-the-artificial-sand-policy-sand-will-now-be-available-for-rs-200-revenue-minister-chandrashekhar-bawankule-a-a1000/</t>
+          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/obcs-will-not-be-treated-unfairly-chandrasekhar-bawankule-answer-to-laxman-haka/939237</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chandrashekhar-bawankule-rejects-obc-reservation-harm-claims-maharashtra-1487524.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A5%82%E0%A4%9A-%E0%A4%B0-%E0%A4%B9%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zbVuE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maratha-aarkshan-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8-%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%AF-%E0%A4%B2%E0%A4%AF-%E0%A4%A8-%E0%A4%B2%E0%A4%A2-%E0%A4%88%E0%A4%B9-%E0%A4%B2%E0%A4%A2%E0%A5%87%E0%A4%B2-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1M3rCj</t>
+          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/good-news-for-farmers-chief-minister-baliraja-panand-roads-scheme-in-maharashtra-chandrashekhar-bawankule-difficulties-will-be-resolved-roads-will-be-built-up-to-the-fields-1382855</t>
+          <t>https://www.msn.com/mr-in/news/other/nagpur-political-news-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B3-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1LZyoY?cvid=68bc9315762a4b358cad5b270e1111ac&amp;ocid=wispr&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/rohit-pawar-slams-chandrashekhar-bawankule-megha-engineering-fine-controversy-135892296.html</t>
+          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/rohit-pawar-attacks-chandrashekhar-bawankule-twitter-proof-mm76</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/nagpur/news/nagpur-bawankule-pawar-advertisement-controversy-update-135869808.html</t>
+          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-videovsd-99-5388756/lite/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/gunaratna-sadavarte-said-after-the-revenue-minister-chandrashekhar-bawankule-meeting-obc-and-maratha-reservation-reaction-on-raj-uddhav-meeting-too-1383063</t>
+          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/rohit-pawar-attacks-chandrashekhar-bawankule-megha-engineering-fine-135887564.html</t>
+          <t>https://www.esakal.com/mumbai/chandrashekhar-bawankule-has-instructed-that-certificates-should-not-be-issued-on-basis-of-documents-to-curb-fake-caste-certificates-mvk02</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/ncp-leader-rohit-pawar-allegations-on-bjp-chandrashekhar-bawankule-claims-90-crore-waived-off/937727</t>
+          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/gunratna-sadavarte-meets-chandrashekhar-bawankule-maratha-reservation-135886852.html</t>
+          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/bharatiya-janata-party-leader-and-minister-chandrashekhar-bawankule-said-that-uddhav-thackeray-has-no-moral-right-to-speak-on-ind-vs-pak-match/921394/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/revenue-minister-chandrashekhar-bawankule-directs-the-administration-to-find-a-solution-to-the-complex-issue-of-sand-temples-and-ancestral-lands-in-the-konkan-region/920713/</t>
+          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/devendra-fadnavis-seriously-accusations-candidature-cancelled-for-2019-assembly-elections-bjp-give-one-more-chance-to-sudhakar-kohale-dk88-rc70</t>
+          <t>https://www.tendernama.com/tender-news/revenue-minister-bawankules-big-announcement-regarding-the-land-fragmentation-act-within-15-days</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/uddhav-thackeray-is-doing-politics-in-the-name-of-cricket-chandrashekhar-bawankule-criticizes-a-a876-c732/amp/</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/bjp-leader-chandrashekhar-bawankule-ridiculed-the-ncps-resolution-declarations-only-to-stop-workers-from-leaving-the-party-rm96-rc70</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/minister-chandrashekhar-bawankule-on-obc-reservation-slams-vijay-wadettiwar/919460/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/jalna-news-%E0%A4%86%E0%A4%AE%E0%A4%A6-%E0%A4%B0-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%B2-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%96-%E0%A4%9F-%E0%A4%B2-%E0%A4%A3-%E0%A4%95%E0%A4%B0/ar-AA1MeEhz</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/jalna/mla-rohit-pawars-allegations-against-bawankule-are-false-lonikar-np88</t>
+          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chandrashekhar-bawankule-critiques-uddhav-thackerays-cricket-politics-1491997.html</t>
+          <t>https://sarkarnama.esakal.com/mumbai/chhagan-bhujbal-fake-kunbi-certificates-controversy-obc-meeting-hn97</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chandrashekhar-bawankule-open-challenge-to-rohit-pawar-in-cm-fadnavis-advertisement-case/articleshow/123777163.cms</t>
+          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/amp/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/cm-fadnavis-baliraja-panand-raste-yojana-for-farmers-a-big-announcement-by-revenue-minister-chandrashekar-bawankule/938221</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/bjps-chandrashekhar-bawankule-slams-uddhav-thackeray-over-india-vs-pakistan-asia-cup-match/</t>
+          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-leader-and-revenue-minister-chandrashekhar-bawankule-s-reaction-to-atul-save-s-meeting-sparks-interest-in-maharashtra-politics-and-current-affairs-1382705</t>
+          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/fine-collection-megha-engineering-issue-bjp-mla-demand-ssb-93-5366746/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%AF%E0%A4%AE-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A4%82%E0%A4%98%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%B5-%E0%A4%B3%E0%A5%82-%E0%A4%A1%E0%A5%87%E0%A4%AA-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6/ar-AA1Df6na?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/gunaratna-sadavarte-warns-of-dragging-radhakrishna-vikhe-patil-to-court-if-cases-against-maratha-protesters-are-withdrawn/920375/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/no-kunbi-caste-certificates-on-fake-documents-instructions-bawanekule-ap84</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://kokansadlive.com/maharashtra/minister-bawankule-reviews-pending-revenue-cases-in-konkan/22713</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrashekhar-bawankule-on-obc-upsamiti-meeting-maratha-reservation-kunbi-certificate-marahi-news-1383083</t>
+          <t>https://www.nagpurtoday.in/bawankules-initiative-five-nagpur-pilgrimage-sites-granted-b-category-status/09191501</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/baliraja-panand-road-scheme-maharashtra-farmers-transport-ab96</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sadavarte-targets-vikhepatil-and-jarange-what-did-he-say-after-meeting-minister-bawankule/videoshow/123811967.cms</t>
+          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-to-chair-crucial-maharashtra-cabinet-sub-committee-meeting-on-obc-and-maratha-reservation-on-september-10-1382547</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-has-made-murum-mining-royalty-free-1484899.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/state/vidarbha/state-government-accepts-m-sand-policy-entrepreneurs-should-produce-quality-artificial-sand-minister-bawankule-directs/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/minister-chandrashekhar-bawankule-on-ncp-sp-rohit-pawar-allegations/919482/</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/mla-deshmukh-demands-new-revenue-offices-in-sangola-taluka-amp17</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/subcommittee-meeting-obc-chandrashekhar-bawankule-ministry-minister-aggressive-obc-reservation-kunbi-maratha-reservation-ssb-93-5364353/</t>
+          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/agriculture/chief-minister-baliraja-panand-raste-yojana-good-news-for-farmers-a-big-announcement-by-revenue-minister-chandrashekar-bawankule-1488863.html</t>
+          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/nagpur-promotes-eco-friendly-m-sand-big-push-for-artificial-sand-units-amp17</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/pankaja-munde-on-obc-reservation-and-chhagan-bhujbal-after-meeting-of-obc-subcommittee/920205/amp</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40154-txt-pune-today-20250917044854</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/mumbai/rohit-pawars-allegations-against-bjp-over-devabhau-advertisement-bawankule-gave-a-befitting-reply-saying/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779/amp</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/maharashtra-government-repaying-the-favour-of-electoral-bond-donations-says-mla-rohit-pawar-in-jibe-at-chandrashekhar-bawankule/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/nagpur/kamthi/nagpur-artificial-sand-for-just-rs-200-information-about-bawankule-15367254</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/why-is-rohit-pawars-stomach-hurting-over-advertisements-expressing-love-for-fadnavis-bawankule-questions/09091016</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917031413</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/mumbai/maharashtra-obc-subcommittee-bhujbal-munde-raise-injustice-issue-ab96</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482/amp</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-cabinet-sub-committee-meeting-tomorrow-at-11-am-with-pankaja-munde-chhagan-bhujbal-gulabrao-patil-to-address-obc-demands-and-doubts-1382731</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/lite/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-quota-row-maharashtra-gr-sparks-dispute-over-eligible-word-revenue-minister-bawankule-assures-no-harm-to-obc-reservation-vadettiwar-demands-clarity-1382623</t>
+          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/false-kunbi-registrations-will-not-be-allowed-bawankule-assures-obcs-15374678</t>
+          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/rohit-pawar-medha-engineering-chandrashekhar-bawankule-saamana-online-news/</t>
+          <t>https://www.msn.com/mr-in/news/other/dhananjay-deshmukh-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%A1-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5-%E0%A4%B9-%E0%A4%A4-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%96%E0%A4%82%E0%A4%A4/ar-AA1An2uc?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chandrashekhar-bawankule-there-will-be-no-injustice-against-obcs-chandrashekhar-bawankule-made-it-clear/</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40193-txt-pune-today-20250918034152</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/rohit-pawar-showed-order-regarding-illegal-mining-of-bawankule-dysp-anjali-krishna-case-politics-036723.html</t>
+          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/lite/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/our-best-wishes-to-the-thackeray-brothers-minister-bawankules-suggestive-statement/</t>
+          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/obc-cabinet-sub-committee-meeting-bawankule-instructions-regarding-incorrect-kunbi-entry-036919.html</t>
+          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/sparks-ignited-in-mva-bjp-state-president-chandrashekhar-bawankules-scathing-criticism/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628/amp</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/cm-fadnavis-inagurated-development-works-worth-rs-335-crore-in-yavatmal/</t>
+          <t>https://www.dainikprabhat.com/now-tribal-lands-will-be-available-on-lease-chandrashekhar-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/mou-between-tata-technology-and-govt-in-the-presence-of-cm-fadnavis-govt/amp/</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/chief-minister-devendra-fadnavis-inaugurates-development-works-worth-rs-335-crore-in-yavatmal-125091400010_1.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.berartimes.com/maharashtra/216432/</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-news-injustice-to-obcs-important-decision-of-the-cabinet-sub-committee/</t>
+          <t>https://www.dainikprabhat.com/pune-news-mine-owners-are-in-trouble-mining-in-mountains-and-hills-banned-revenue-minister-bawankules-firm-stance/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/there-will-be-a-radical-change-in-the-lives-of-tribals-devendra-fadnavis/</t>
+          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2-%E0%A4%B2%E0%A5%8B%E0%A4%95-%E0%A4%85%E0%A4%A6%E0%A4%BE%E0%A4%B2%E0%A4%A4%E0%A5%80%E0%A4%B8-%E0%A4%A8%E0%A4%BE%E0%A4%97%E0%A4%B0%E0%A4%BF%E0%A4%95/117148/</t>
+          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/chief-minister-devendra-fadnavis-41/</t>
+          <t>https://www.dainikprabhat.com/shivbhojan-thali-the-shivbhojan-thali-of-uddhav-thackerays-era-will-continue-bawankule-clearly-stated/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/chhagan-bhujbal-expresses-ange-and-demands-cancellation-of-hyderabad-gr-related-to-kunbi-records-in-first-maharashtra-obc-subcommittee-meeting-as11</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrasehkhar-bawankule-chief-minister-baliraja-panand-road-scheme-chandrasekhar-bawankules-announcement-farmers-will-benefit/920043/</t>
+          <t>https://dainikekmat.com/%E0%A4%86%E0%A4%A6%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%B8%E0%A5%80%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%AD%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%A4/118039/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/industry-minister-uday-samant-position-on-reservation-issues-personal-question-of-bhujbal-minister-samant-ar84</t>
+          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%AD%E0%A4%B0%E0%A4%BE%E0%A4%A4%E0%A5%80%E0%A4%B2-%E0%A5%A7%E0%A5%A8-%E0%A4%B9%E0%A4%9C%E0%A4%BE%E0%A4%B0-%E0%A5%AC%E0%A5%A6%E0%A5%A6-%E0%A4%B8/118036/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://aimamedia.org/newsdetails.aspx?nid=503492</t>
+          <t>https://www.msn.com/mr-in/news/other/banjara-reservation-%E0%A4%AC%E0%A4%82%E0%A4%9C-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%9A-%E0%A4%A8-%E0%A4%82%E0%A4%A6/ar-AA1MArpW</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/union-minister-nitin-gadkari-given-name-of-late-congress-leader-shrikant-jichkar-to-flyover-in-nagpur-zws-70-5369897/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8%E0%A4%B5%E0%A4%B0-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%A4-%E0%A4%B2-%E0%A4%97%E0%A4%B0%E0%A4%AC-%E0%A4%AB%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%A4%E0%A4%AA-%E0%A4%B8-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A4%A6%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%B9-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MWJzB</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/obc-reservation-there-will-be-no-injustice-to-obcs-no-false-entries-important-decisions-taken-in-the-meeting-chaired-by-bawankule/920275/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-warns-rohit-pawar-about-allegations-of-90-crores-fine-waived-for-a-company-css-98-5358778/</t>
+          <t>https://divyamarathi.bhaskar.com/amp/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%A1%E0%A4%AA-%E0%A4%A3-%E0%A4%95%E0%A4%B0%E0%A4%A4%E0%A4%82%E0%A4%AF-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%86%E0%A4%B0-%E0%A4%AA-90-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%B6-%E0%A4%AD-%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8/ar-AA1M6js8</t>
+          <t>https://www.saamana.com/chhagan-bhujbal-demands-probe-into-fake-obc-certificates/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/cm-devendra-fadnavis-maharashtra-is-my-adopted-state-committed-to-yavatmal-development-vsb99</t>
+          <t>https://www.lokmat.com/agriculture/news/revenue-ministers-big-announcement-on-the-excavation-of-murum-for-the-repair-of-panand-roads-in-the-state-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/vidarbha/cm-devendra-fadnavis-maharashtra-is-my-adopted-state-committed-to-yavatmal-development-vsb99</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/aap-chandrapur.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/politics/there-will-be-no-injustice-to-obcs-caste-certificate-should-be-issued-only-after-verification-bawankules-instructions-in-the-obc-sub-committee-meeting-05-696385</t>
+          <t>https://lokmat.news18.com/videos/video/vijay-wadettiwar-vs-chandrashekhar-bawankule-reservation-gr-wadettiwar-s-elgar-marathi-news-1075795.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/78454/</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/there-will-be-no-injustice-to-obcs-kunbi-certificate-only-after-matching-the-lineage/116660/</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-uddhav-thackeray-cricket-row-uddhav-thackeray-criticized-over-operation-sindoor-absence-pakistan-flags-and-politicizing-india-pakistan-match-maharashtra-government-firm-on-obc-reservation-1383972</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-letest-marathi-news-update-15-sept-2025-maharashtra-politics-ram-satpute-dhananjay-munde-banjara-community-anajali-damania-rohit-pawar-pune-politics-manoj-jarange-patil-chandrashekhar-bawankule-ashish-shelar-uddhav-thackeray-as11</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/chandrashekhar-bawankule-post-on-x-targeting-mla-rohit-pawar/938538</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-local-body-polls-chandrashekhar-bawankule-on-ticket-distribution-public-opinion-to-decide-candidates-amidst-chandrapur-factionalism-1385673</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/uddhav-thackeray-is-doing-politics-in-the-name-of-cricket-chandrashekhar-bawankule-criticizes-a-a876-c732/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-maratha-reservation-controversy-bhujbal-bawankule-response-1489644.html</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-megha-engineering-fine-waiver-row-rohit-pawar-bawankule-clash-intensifies-as-government-documents-reveal-fine-from-radhakrishna-vikhe-patil-s-tenure-1382711</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-govt-to-prevent-forgery-in-maratha-kunbi-certificates-sub-committee-demands-2900-crore-for-obc-ministry-welfare-schemes-1384585</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maratha-reservation-two-petitions-filed-in-bombay-high-court-against-state-government-notification-approving-implementation-of-hyderabad-gazetteer-maharashtra-marathi-news-1383163/amp</t>
+          <t>https://www.navakal.in/maharashtra/vishwa-hindu-parishadno-muslims-allowed-in-garba-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thane-politics-ganesh-naik-s-ravana-attack-on-eknath-shinde-sparks-mahayuti-discord-ahead-of-thane-municipal-corporation-elections-1383104/amp</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/navratri-utsav-only-hindus-allowed-in-garbhas-vishva-hindu-parishad-takes-this-stand/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/maharashtra-revenue-minister-chandrashekhar-bawankule-on-maratha-reservation-there-will-be-no-injustice-with-obc/4135300/</t>
+          <t>https://www.business-standard.com/amp/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/minister-bawankule-slams-rahul-gandhi-over-election-commission-allegations-1351292.html/amp</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-tribal-land-lease-policy-chandrashekhar-bawankule-announcement-1361630.html/amp</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/14/chandrashekhar-bawankule-big-statement-there-will-be-no-injustice-with-obc-maratha-reservation-news-khabar-24-express/</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/13/cm-devendra-fadnavis-chandrashekhar-bawankule-initiative-gives-new-momentum-to-nagpur-development-khabar-24-express/</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/13/devendra-fadnavis-chandrashekhar-bawankule-initiative-modern-skill-development-center-opens-in-ramtek-khabar-24-express/</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-government-allows-tribal-farmers-to-lease-land-to-private-companies-1362201.html/amp</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/14/chandrashekhar-bawankule-big-statement-there-will-be-no-injustice-with-obc-maratha-reservation-news-khabar-24-express/chandrashekhar-bawankule-big-statement-there-will-be-no-injustice-with-obc-maratha-reservation-news-khabar-24-express/</t>
+          <t>https://navbharatlive.com/maharashtra/ncp-sharad-pawar-evm-demo-bawankule-reaction-1356810.html/amp</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/desh/maharashtra-marathi-live-news-14-september-2025-maharashtra-weather-updates-marathi-sahitya-sammelan-ind-vs-pak-asia-cup-2025-zp-presidentship-reservation-nepal-violence-gold-silver-rate-maratha-obc-reservation-manoj-jarange-cm-devendra-fadnavis-stock-market-ajit-pawar-eknath-shinde-pm-narendra-modi-rahul-gandhi-farmer-railway-sports-entertainment-politics-finance-trending-viral-upsc-mpsc-news-updates</t>
+          <t>https://www.lokmat.com/agriculture/farming-ideas/latest-news-see-what-bhandara-district-farmers-did-to-control-the-khodkid-of-crops-read-in-detail-a-a993/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371/amp</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/visual-storytelling-mumbai-obc-leaders-meeting-against-maratha-reservation-hyderabad-gazette-sdp-92-5365685/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/market-yard/latest-news-kanda-market-red-onions-arrive-in-lasalgaon-market-see-market-prices-a-a993/</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-septembar-10-political-news-in-marathi-938172</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-pankaja-munde-firm-stance-opposition-to-issuing-fake-kunbi-certificates-manoj-jarange-patil-maratha-reservation/articleshow/123806119.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/cm-devendra-fadnavis-and-nitin-gadkari-meet-shrikant-jichkar-mother-in-nagpur-program/articleshow/123854763.cms</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=3&amp;liveblog_last=90890-1757948209</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/seven-friends-from-nagpur-returned-from-nepal-and-shared-their-thrilling-experience/articleshow/123848579.cms</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90863-1757936847</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/pimpri-chinchwad/todays-latest-marathi-news-pne25l38633-txt-pc-today-20250914110635</t>
+          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/premier/naam-foundation-celebrates-its-10th-anniversary-in-presence-of-minitster-nitin-gadkari-entertainment-news-kds07</t>
+          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/lite/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/information/mukhyamantri-baliraja-panand-raste-yojana-launched-03-696277</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/tragic-incident-two-teen-boys-drown-in-pond-while-taking-photos-families-devastated-community-in-shock-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/pankaja-munde-maratha-reservation-white-paper-demand-maratha-reservation-news-chhagan-bhujbal-9251415</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/buldhana-farmers-threaten-mass-movement-if-government-fails-to-announce-wet-drought-bdk97</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-fear-deputy-cm-eknath-shinde-chhatrapati-sambhajinagar-visit-review-jp75</t>
+          <t>https://vishwanewsmarathi.com/big-news-garba-only-for-hindus-vhps-conditions/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-political-crime-sports-national-international-business-entertainment-lifestyle-breaking-news-982812.html</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/maratha-kunbi-certificates-should-be-issued-only-after-thorough-verification-decision-taken-in-obc-ministry-sub-committee-meeting-05-697489</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-9th-september-2025-marathi-live-updates-ajit-pawar-lalbaugcha-raja-mandal-manoj-jarange-patil-maratha-reservation/liveblog/123776681.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/mahadev-koli-community-protests-hyderabad-gazette-black-flags-on-muktisangram-day-jp75</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bhujbal-aggressive-in-obc-subcommittee-meeting-alleges-more-funds-given-to-maratha-community-objects-to-kunbi-records-gr-283714/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/maharashtra-government-explanation-in-high-court-on-pil-file-against-ladki-bahin-yojana/articleshow/123832832.cms</t>
+          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/lite/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/4/?m=0</t>
+          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/pm-modi-political-retirement-bjp-president-ravindra-chavan-reaction-dk88-rc70</t>
+          <t>https://saamtv.esakal.com/amp/story/sports/suryakumar-yadav-team-to-take-to-the-field-against-oman-today-will-the-players-on-the-bench-get-a-chance-sjk95</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE-%E0%A4%9C-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%B6-11-%E0%A4%B5%E0%A4%B0%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%A6-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%B0-%E0%A4%9C-%E0%A4%A8-%E0%A4%AE-%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%9A-%E0%A4%AE%E0%A5%81%E0%A4%B9%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A4-%E0%A4%A0%E0%A4%B0%E0%A4%B2/ar-AA1MeDFB</t>
+          <t>https://news34.in/2025/09/chanda-revenue-mitra-chatbot-launch-chandrapur/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/obc-reservation/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-rss-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1HLd3n?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://dainikmaval.com/baliraja-shet-panand-road-scheme-to-be-launched-with-special-campaign-from-17th-to-22nd-september/</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/11/maratha-quota-mah-govt-starts-hyderabad-gazette-implementation-process-no-impact-on-obc-reservation.html</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/maha-revenue-dept-allocates-land-for-ibs-residential-quarters-in-panvel-1004893</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://housing.com/news/maharashtra-stamp-act-an-overview-on-stamp-duty-on-immovable-property/</t>
+          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/ajchya-tajya-batmya-maharashtra-marathi-latest-live-news-updates-12th-september-2025-maratha-obc-aarkashan-clash-maharashtra-weather-mumbai-thane-nagpur-pune-nashik-weather-forecast-rain-update-live-news-today-pune-local-crime-top-headlines</t>
+          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/centre-important-schemes-to-bring-tribal-community-into-mainstream-of-development-says-cm-devendra-fadnavis-zws-70-5370140/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-crime-news-unknown-assailants-shot-on-businessman-and-robbed-him-of-cash-worth-lakhs/articleshow/123815444.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom27-mh-tribals-ld-land-lease.amp.html</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/09/maha-cm-dy-cm-and-other-leaders-wish-radhakrishnan-on-his-victory/</t>
+          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/PressReleseDetailm.aspx?PRID=2166159</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maharashtra-govt-scheme-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%86%E0%A4%A3%E0%A4%96-%E0%A4%8F%E0%A4%95-%E0%A4%AE-%E0%A4%A0-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%A6-%E0%A4%B2-a-to-z-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4/ar-AA1Mfl2g</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/babanrao-lonikar-news-rohit-pawar-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%96-%E0%A4%9F-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A5%81%E0%A4%B0%E0%A4%B5%E0%A4%B2-%E0%A4%B2-%E0%A4%A3-%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95-%E0%A4%86%E0%A4%B0-%E0%A4%AA-%E0%A4%95-%E0%A4%AF-n18v/vi-AA1Mbu5E</t>
+          <t>https://www.lokmat.com/agriculture/weather/the-rains-will-stop-the-monsoons-return-journey-will-begin-how-do-you-know-when-the-monsoon-will-leave-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/latur/atur-news-renapur-tehsildar-prashant-thorat-suspension-cancelled-ng81</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%A4-%E0%A4%A1%E0%A4%AA-%E0%A4%A3-%E0%A4%95%E0%A4%B0%E0%A4%A4%E0%A4%82%E0%A4%AF-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%96%E0%A4%B3%E0%A4%AC%E0%A4%B3%E0%A4%9C%E0%A4%A8%E0%A4%95-%E0%A4%86%E0%A4%B0-%E0%A4%AA-90-%E0%A4%95-%E0%A4%9F-%E0%A4%82%E0%A4%B5%E0%A4%B0%E0%A5%81%E0%A4%A8-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%B6-%E0%A4%AD-%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A4%82%E0%A4%A8%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8/ar-AA1M6js8?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-latest-live-news-updates-20th-september-2025-sharad-pawar-jayant-patil-gopichand-padalkar-bjp-ncp-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-live-news-today-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mum25i33727-txt-mumbai-20250909042858</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-obc-subcommittee-bhujbal-munde-raise-injustice-issue-ab96</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/baliraja-panand-raste-scheme/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://mondaytomondaynews.com/what-is-mukhyamantri-baliraja-panand-raste-yojana-maharashtra-government/</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://hellomaharashtra.in/mukhyamantri-baliraja-raste-panand-yojana-launched/</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/vhp-says-only-hindus-allowed-at-garba-events-congress-slams-divisive-agenda-207684</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/how-many-obc-certificates-have-been-issued-so-far-release-all-the-information-by-publishing-a-white-paper/116657/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/obc-community-s-concerns-over-reservation-will-not-be-ignored-minister-pankaja-munde/2901852</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/no-injustice-to-obcs-kunbi-certificates-to-be-issued-only-after-due-verification-bawankule-10084145</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpurs-gyanyogi-jichkar-bridge-closed-on-the-second-day-of-inauguration-citizens-angry/09132030</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/bjp-targets-51-percent-in-local-bodies-election-said-chandrashekhar-bawankule-a-a382-c719/?utm_source=Lokmat.com&amp;utm_medium=shorts_desktop_headline</t>
+          <t>https://chandablast.com/?p=51003</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/cyber-criminals-cheated-bank-officer-and-his-family-of-rupees-39-lakh-in-nagpur/articleshow/123835223.cms</t>
+          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-videovsd-99-5388756/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/mukhyamantri-baliraja-panand-roads-scheme-transportation-problem-agriculture-maharashtra-farmers-benifits-mvk02</t>
+          <t>https://ahmednagarlive24.com/spacial/maharashtra-news-at-this-time-20-districts-and-81-talukas-will-be-formed-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/hsrp-number-plate-man-pil-dismissed-by-nagpur-court-over-extra-fee-in-maharashtra-than-other-states/articleshow/123805572.cms</t>
+          <t>https://www.newsdrum.in/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move-10483282</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/gulabrao-patil-statement-on-maratha-obc-reservation-dispute-manoj-jarange-maharashtra-caste-politics-vsd-99-5359013/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/kokan/sindhudurg/nilesh-rane-demands-separate-sand-policy-for-traders-in-konkan-review-meeting-sp96</t>
+          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/amravati-district-ajay-gaur-stranded-amid-nepal-violence-recounts-terrifying-experience/articleshow/123800988.cms</t>
+          <t>https://pudhari.news/maharashtra/mumbai/vhp-navratri-garba-entry-hindus-only-ab96</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-opposes-maratha-caste-certificate-gr-maharashtra-1489591.html</t>
+          <t>https://www.loksatta.com/nashik/ex-bjp-corporator-arrested-nashik-law-and-order-amid-political-unrest-panchvati-shooting-case-vsd-99-5388883/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-govt-a-new-revolutionary-decision-for-farmers-but-what-will-actually-happen/</t>
+          <t>https://www.loksatta.com/nashik/nashik-traffic-diversions-announced-navratri-celebrations-kalika-mata-renuka-devi-temples-vsd-99-5388871/lite/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/training-facility-for-3-thousand-students-skill-development-center-in-nagpur-by-tata-technology/132222/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/gopichand-padalkar-no-apology-statement-ng81</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178359/</t>
+          <t>https://www.loksatta.com/nashik/uddhav-thackeray-shiv-sena-restructures-jalgaon-ahead-local-body-elections-new-appointments-vsd-99-5388810/lite/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/178382/</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpurs-gnyanyogi-jichkar-bridge-closed-a-day-after-inauguration/09132031</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/farmers-should-stay-strong-avoid-suicides-adopt-natural-farming-sri-sri-ravi-shankar-mj18</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/amp_articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/maha-revenue-dept-allocates-land-ib-s-residential-quarters-panvel-450341</t>
+          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/amp/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/farming-ideas/baliraja-shet-panand-road-scheme-will-gain-momentum-in-the-state-now-strong-roads-will-be-built-a-a975/</t>
+          <t>https://www.deccanherald.com/amp/story/india%2Fmaharashtra%2Fvhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-to-host-farmers-fair-focused-on-sustainable-agriculture/articleshow/123793282.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/amp_articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://english.bombaysamachar.com/national/listening-to-morari-bapus-ram-katha-is-a-blessing-equal-to-chanting-the-sahasranama-cm-devendra-fadnavis/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/agriculture/gis-technology-for-village-side-road-in-maharashatra-digital-record-of-panand-farm-road-1492047.html</t>
+          <t>https://pudhari.news/amp/story/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/obc-vs-maratha-quota-minister-chhagan-bhujbal-slams-move-exposes-fault-lines-in-maharashtra-government-2785432-2025-09-11</t>
+          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/marathas-vs-obcs-reservation-issue-heads-to-courts-3717455</t>
+          <t>https://divyamarathi.bhaskar.com/national/news/orders-to-sprinkle-cow-urine-on-people-during-garba-in-maharashtra-135974133.html</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/reservation-issue-becomes-wider-in-maharashtra-even-as-govt-grapples-with-maratha-vs-obc-quota-problem-3723032</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/obc-communitys-concerns-over-reservation-will-not-be-ignored-minister-pankaja-munde-10068428</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maratha-reservation-fadnavis-statement-reservation-not-to-anyone-in-general-but-to-marathas-who-have-a-valid-proof-of-kunbi</t>
+          <t>https://marathi.indiatimes.com/e-paper/amit-shah-declares-bokaro-in-jharkhand-maoist-free/articleshow/123916647.cms</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/dont-try-to-challenge-hyderabad-gazette-in-court-otherwise-you-lost-16-percent-obc-reservation-maratha-leader-manoj-jarange-patil-warn-to-chhagan-bhujbal-1488289.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/trimbakeshwar-womens-pot-protest-against-water-shortage/articleshow/123916850.cms</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/there-will-be-no-injustice-to-obcs-no-false-records-important-decision-taken-in-the-cabinet-sub-committee-meet.amp.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/obcs-elgar-hakes-protest-in-baramati-certificate-will-not-be-available-just-on-the-gazette-bawankule-135851615.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ncp-chhagan-bhujbal-criticizes-governments-procedure-regarding-manoj-jarange-patil-maratha-reservation-gr/articleshow/123830074.cms</t>
+          <t>https://www.dainikprabhat.com/wagholi-news-wadebolhai-gram-panchayat-gets-aap-sarkar-seva-kendra/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/maratha-community-should-not-be-given-bogus-certificates-pankaja-munde-stand-in-obc-subcommittee-meeting-283722/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-action-will-be-taken-against-bogus-documents-decision-of-obc-cabinet-sub-committee-meeting-under-discussion/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/bhujbal-aggressive-in-obc-subcommittee-meeting-alleges-more-funds-given-to-maratha-community-objects-to-kunbi-records-gr-283714/amp/</t>
+          <t>https://www.timemaharashtra.com/politics/a-conspiracy-has-been-hatched-to-defame-laxman-hake-vijay-vadettiwar-claims/133273/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/obc-leaders-furious-over-maratha-reservation/</t>
+          <t>https://news34.in/2025/09/chandrapur-obc-leaders-statements-2025/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/congresss-journey-is-a-history-of-injustice-against-the-obc-community.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-rotary-underground-market-planned-at-medical-square-gadkari/articleshow/123858415.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/gadkari-fadnavis-to-inaugurate-rto-flyover-today/articleshow/123836339.cms</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178345/</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/178405/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178401/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/vidarbha/yevatmal/tribal-life-transformation-next-3-years-cm-devendra-fadnavis-mk94</t>
+          <t>https://www.lokmat.com/agriculture/farming-ideas/karnataka-on-the-lines-of-andhra-pradesh-a-a975/amp/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/state-government-help-loss-affected-farmers-cm-devendra-fadnavis/</t>
+          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/after-bhujbal-sena-minister-gulabrao-patil-opposes-gr-on-marathas/articleshow/123724181.cms</t>
+          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/maratha-quota-govt-starts-hyderabad-gazette-implementation-process-3270003/</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/13/nagpur-to-be-hub-of-solar-panel-manufacturing-cm-fadnavis.html</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-to-get-rs115cr-skill-development-centre-tata-signs-mou-with-state/articleshow/123869977.cms</t>
+          <t>http://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%AF%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%A4-%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%AB-%E0%A4%AF%E0%A4%A6%E0%A5%87-%E0%A4%B5-%E0%A4%9A%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%A8-%E0%A4%9C-%E0%A4%B2/ar-AA1MvyUA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://policenama.com/adachiwadi-village-news-pune-adachiwadi-in-purandar-taluka-a-new-example-emerged-as-a-model-village-videos/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom38-mh-garba-ld-vhp.amp.html</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-biz-hub-to-take-shape-in-phased-manner-over-15-years/articleshow/123772865.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/marathas-should-not-be-given-fake-kunbi-certificates-maha-minister-450832</t>
+          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://english.bombaysamachar.com/national/cm-fadnavis-inaugurated-and-performed-foundation-stone-laying-of-development-works-worth-%E2%82%B9335-crore-in-yavatmal/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-approves-4-hectares-in-panvel-for-sib-residential-quarters</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://english.bombaysamachar.com/national/cm-fadnavis-inaugurated-and-performed-foundation-stone-laying-of-development-works-worth-%E2%82%B9335-crore-in-yavatmal/?amp=1</t>
+          <t>https://indianexpress.com/article/political-pulse/maratha-quota-fadnavis-govt-catch-22-floodgates-demands-10258572/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178292/</t>
+          <t>http://www.msn.com/en-in/news/India/maratha-quota-row-rumblings-in-mahayuti-alliance-chhagan-bhujbal-skips-cabinet-meet/ar-AA1LQ2jJ?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/No-injustice-to-OBCs-Kunbi-certificates-to-be-issued-only-after-due-verification-Bawankule/2902881</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom30-mh-obc-committee-certificates.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/the-free-press-journal/20250911/281595246673030</t>
+          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-accused-of-fake-maratha-kunbi-caste-certificate-documents-manoj-jarange-patil-1494274.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/rohit-pawar-ncp-sp-allegations-of-200-crore-corruption-tagged-ajit-pawar/919533/</t>
+          <t>https://www.deccanherald.com/amp/story/india%2Fmaharashtra%2Ftribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://newstown.in/obc-leader-chhagan-bhujbal-critisized-government-for-bypassing-procedure-while-issuing-gr-on-maratha-reservation-objects-word-relationship/</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/finally-rto-flyover-to-open-on-friday/articleshow/123793290.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-court-cracks-down-on-underage-driving-woman-fined-%E2%82%B932500/09081750</t>
+          <t>https://www.msn.com/en-in/autos/photos/velhe-taluka-in-pune-renamed-after-chhatrapati-shivajis-first-capital-fort-rajgad/ar-AA1KZLQZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AF-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%A4-%E0%A4%A4%E0%A4%AF-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4%E0%A4%82%E0%A4%AF-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%B8-%E0%A4%B0%E0%A4%96%E0%A4%82-%E0%A4%A8%E0%A4%B5%E0%A4%82-%E0%A4%B6%E0%A4%B9%E0%A4%B0-1710-%E0%A4%B9%E0%A5%87%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A4%B0%E0%A4%B5%E0%A4%B0-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%89%E0%A4%AD-%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%9C%E0%A4%97-%E0%A4%B0-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%82%E0%A4%A7/ar-AA1M6Vog</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/fix-the-loopholes-in-quota-gr-says-bhujbal-101757531207674.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/10/maratha-reservation-gr-to-be-implemented-in-a-time-bound-manner.html</t>
+          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/what-is-mukhyamantri-baliraja-panand-raste-yojana-marathi-agriculture-news-1476799.html</t>
+          <t>https://chandablast.com/?p=50509</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/market-yard/latest-news-international-market-committee-will-be-built-in-ahilyanagar-district-cost-of-15-crores-a-a993/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90839-1757925166</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-8th-september-2025-marathi-batmya-lalbaugcha-raja-visarjan-raj-uddhav-thackeray-brothers-dasara-melava-chandra-grahan-lunar-eclipse/liveblog/123755669.cms</t>
+          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/deputy-cm-ajit-pawar-on-reports-of-cm-devendra-fadnavis-disappointment-over-ips-anjana-krishna-case/938959/amp</t>
+          <t>https://www.berartimes.com/vidarbha/216594/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/spontaneous-response-to-maha-bhandara-in-nallasopara-and-virar-on-the-occasion-of-anant-chaturdashi-more-than-.html</t>
+          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/8/sanjay-raut-feels-blessed-to-visit-afzal-khans-grave.html</t>
+          <t>https://www.indiejournal.in/article/sakshep-eci-vote-chori-controversy</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/amp/india-news/himachal-rains-death-toll-rises-to-427-243-rain-related-184-in-accidents-125092000391_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>https://thefocusindia.com/maharashtra-news/mou-between-maharashtra-government-and-naam-foundation-284511/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/kunbi-caste-certificate-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%AC-%E0%A4%97%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%96-%E0%A4%B2-%E0%A4%AA%E0%A4%A1%E0%A4%A4-%E0%A4%B3%E0%A4%A3/ar-AA1MHcDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>https://agrowon.esakal.com/agro-special/khadgaon-farmer-suicide-case-inquiry-report-submitted-to-collector-mj18</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>https://ratnagirikhabardar.com/news/79889/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/law-order/3634600-maharashtras-new-lease-law-a-boon-or-bane-for-tribal-farmers</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2933cr-pending-funds-10470839</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha-local-body-polls/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ssubt-fears-rigging-tampering-with-voter-list-in-maha-local-body-polls</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/pune/7500-students-take-cleanliness-pledge-in-pune-to-mark-pm-modis-75th-birthday/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/vidarbha/nagpur/global-level-tourist-destination-to-come-up-at-koradi-mou-signed-in-presence-of-cm-sdj87</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/detail/national/Maharashtra-OBC-panel-orders-strict-scrutiny-of-caste-certificates-clears-Rs-2-933cr-pending-funds/2920779</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>https://www.timemaharashtra.com/maharashtra/navratri-new-decision-from-vishwa-hindu-parishad-aadhaar-card-mandatory-to-watch-garba-during-navratri/133217/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>https://www.outlookindia.com/amp/story/national/vhp-says-only-hindus-should-be-allowed-at-garba-sparks-political-row-in-maharashtra</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A289"/>
+  <dimension ref="A1:A219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,2016 +438,1526 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179502/</t>
+          <t>https://mahasamvad.in/178572/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/land-approved-for-bhandara-judges-residence-revenue-minister-chandrashekhar-bawankules-initiative.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418/amp</t>
+          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-video-vsd-99-5388756/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-plans-law-to-lease-tribal-barren-land-to-private-companies</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%81%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%AE%E0%A5%87%E0%A4%97-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AF-%E0%A4%97-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%9D%E0%A4%97%E0%A4%A1-%E0%A4%B8%E0%A5%81%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AE-%E0%A4%A0-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1MeEni?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179430/</t>
+          <t>https://www.loksatta.com/nagpur/revenue-minister-bawankules-announcement-in-gadchiroli-phm-00-5385317/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-video-vsd-99-5388756/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://chandablast.com/?p=50932</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/malegaon-revenue-minister-chandrashekhar-bawankule-grampanchayats-land/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/21/maharashtra-knows-what-lights-vadettiwar-lit-when-he-was-a-minister-minister-chandrashekhar-bawankule-criticiz.html</t>
+          <t>https://mpbreakingnews.in/marathi/politics/new-districts-in-maharashtra-chandrashekhar-bawankule-big-statement-03-698118</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178572/</t>
+          <t>https://www.thebridgechronicle.com/news/government-aims-transform-pune-world-class-infrastructure-chandrashekhar-bawankule-agn97</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%95%E0%A4%A1%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A4%B9-%E0%A4%B2%E0%A4%82-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A4%E0%A5%8D%E0%A4%AF%E0%A5%81%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A4%B0-%E0%A4%95-%E0%A4%81%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8%E0%A4%9A-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A5%87%E0%A4%96-%E0%A4%95%E0%A4%B0%E0%A4%A4-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1yazrQ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/revenue-minister-bawankules-announcement-in-gadchiroli-phm-00-5385317/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-tribal-farmers-land-leasing-income-boost</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-encroachment-on-farm-roads-to-be-cleared-govt-to-map-such-pathways-says-bawankule/ar-AA1MXpLZ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439/amp</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1292529</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/farming-ideas/revenue-ministers-big-announcement-on-the-excavation-of-murum-for-the-repair-of-panand-roads-in-the-state-a-a975/amp/</t>
+          <t>https://theprint.in/india/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister/2747478/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852/amp</t>
+          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/politics/new-districts-in-maharashtra-chandrashekhar-bawankule-big-statement-03-698118</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/officials-should-act-without-condoning-any-wrongdoing/</t>
+          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3634952-controversy-brews-over-garba-entry-restrictions-amidst-navratri-celebrations?amp</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Tribals-in-Maharashtra-can-now-lease-barren-land-to-private-entities;-govt-to-bring-law-Minister/2932964</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1292529</t>
+          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2-933cr-pending-funds/2920779</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining?amp</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bes11-mh-bawankule-farmers.amp.html</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bawankule-backs-organisers--rights--wadettiwar-slams-move/2932800</t>
+          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bjp-minister-backs-organisers--rights--cong-slams-move/2934001</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/No-opposition-to-Badgujar-s-induction-into-BJP-Fadnavis/2655228</t>
+          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers?amp</t>
+          <t>https://mahasamvad.in/178575/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom22-mh-tribals-land-lease.amp.html</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3634600-maharashtras-new-lease-law-a-boon-or-bane-for-tribal-farmers?amp</t>
+          <t>https://www.esakal.com/pune/chandrashekhar-bawankule-slams-uddhav-thackeray-says-opposing-reservation-is-wrong-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
+          <t>https://pudhari.news/maharashtra/pune/chief-minister-focus-pune-development-chandrashekhar-bawanakule-sb97</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
+          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bes11-mh-bawankule-farmers.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers</t>
+          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809-amp.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840-amp.html</t>
+          <t>https://www.saamana.com/chandrashekhar-bawankule-says-government-got-proposal-for-20-new-district/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/chandrashekhar-bawankule-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B9-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%9C%E0%A4%96%E0%A4%AE%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%AE-%E0%A4%A0-%E0%A4%9A-%E0%A4%B3%E0%A5%82-%E0%A4%A8%E0%A4%AF%E0%A5%87-%E0%A4%95%E0%A5%83%E0%A4%B7-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95-%E0%A4%95-%E0%A4%9F%E0%A5%87-%E0%A4%95-%E0%A4%B9-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%B8%E0%A4%A4-%E0%A4%B2-%E0%A4%A4%E0%A4%B0-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A4%E0%A4%B0%E0%A5%8D%E0%A4%AB%E0%A5%87-%E0%A4%86%E0%A4%AE%E0%A5%8D%E0%A4%B9-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%AE-%E0%A4%AE-%E0%A4%97%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1Cn5Cg?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
+          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
+          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://www.esakal.com/mumbai/chandrashekhar-bawankule-has-instructed-that-certificates-should-not-be-issued-on-basis-of-documents-to-curb-fake-caste-certificates-mvk02</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrashekhar-bawankule-slams-uddhav-thackeray-says-opposing-reservation-is-wrong-politics-pjp78</t>
+          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
+          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178575/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
+          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/chandrasekhar-bavankule-bhandara-districts-guardian-minister/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/nagpur/chandrasekhar-bavankule-bhandara-districts-guardian-minister/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/chhagan-bhujbal-fake-kunbi-certificates-controversy-obc-meeting-hn97</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/cctvs-gardens-and-sports-grounds-instruction-chandrasekhar-bavankules-interaction/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/nagpur/cctvs-gardens-and-sports-grounds-instruction-chandrasekhar-bavankules-interaction/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/22/relief-due-to-gst-reforms-common-people-benefit-from-reduction-in-tax-rates-on-daily-use-items-revenue-ministe.amp.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
+          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
+          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%B8%E0%A5%81%E0%A4%B0%E0%A5%82%E0%A4%9A-%E0%A4%B0-%E0%A4%B9%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B8%E0%A5%8D%E0%A4%AA%E0%A4%B7%E0%A5%8D%E0%A4%9F-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1zbVuE?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
+          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/nagpur-political-news-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B3-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A8-%E0%A4%82%E0%A4%A6-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B9-%E0%A4%AE%E0%A4%B9%E0%A4%B8%E0%A5%82%E0%A4%B2%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87/ar-AA1LZyoY?cvid=68bc9315762a4b358cad5b270e1111ac&amp;ocid=wispr&amp;apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://www.esakal.com/pune/vision-for-pune-transforming-into-indias-top-infrastructure-hub-chandrashekhar-bawankule-pjp78</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-videovsd-99-5388756/lite/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
+          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/chandrashekhar-bawankule-has-instructed-that-certificates-should-not-be-issued-on-basis-of-documents-to-curb-fake-caste-certificates-mvk02</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AF%E0%A4%95%E0%A4%B5-%E0%A4%A1-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%B8-%E0%A4%AA%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%9D%E0%A5%87%E0%A4%A1%E0%A4%AA-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A4%82%E0%A4%9A-%E0%A4%AF%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%82%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%B5-%E0%A4%A6%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1N0sRo?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917024051</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/tender-news/revenue-minister-bawankules-big-announcement-regarding-the-land-fragmentation-act-within-15-days</t>
+          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/vidarbha/bjp-leader-chandrashekhar-bawankule-ridiculed-the-ncps-resolution-declarations-only-to-stop-workers-from-leaving-the-party-rm96-rc70</t>
+          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
+          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/chhagan-bhujbal-fake-kunbi-certificates-controversy-obc-meeting-hn97</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40193-txt-pune-today-20250918034152</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/amp/</t>
+          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8-%E0%A4%AF%E0%A4%AE-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%89%E0%A4%B2%E0%A5%8D%E0%A4%B2%E0%A4%82%E0%A4%98%E0%A4%A8-%E0%A4%95%E0%A5%87%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%B5-%E0%A4%B3%E0%A5%82-%E0%A4%A1%E0%A5%87%E0%A4%AA-%E0%A4%B0%E0%A4%A6%E0%A5%8D%E0%A4%A6/ar-AA1Df6na?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
+          <t>https://ratnagirikhabardar.com/news/79258/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
+          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankules-initiative-five-nagpur-pilgrimage-sites-granted-b-category-status/09191501</t>
+          <t>https://www.dainikprabhat.com/pune-news-mine-owners-are-in-trouble-mining-in-mountains-and-hills-banned-revenue-minister-bawankules-firm-stance/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
+          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-has-made-murum-mining-royalty-free-1484899.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/chandrashekhar-bawankule-praises-new-gst-reform/133431/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
+          <t>https://ratnagirikhabardar.com/news/79689/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
+          <t>https://www.saamana.com/chhagan-bhujbal-demands-probe-into-fake-obc-certificates/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
+          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/aap-chandrapur.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40154-txt-pune-today-20250917044854</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-letest-marathi-news-update-15-sept-2025-maharashtra-politics-ram-satpute-dhananjay-munde-banjara-community-anajali-damania-rohit-pawar-pune-politics-manoj-jarange-patil-chandrashekhar-bawankule-ashish-shelar-uddhav-thackeray-as11</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779/amp</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-local-body-polls-chandrashekhar-bawankule-on-ticket-distribution-public-opinion-to-decide-candidates-amidst-chandrapur-factionalism-1385673</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-govt-to-prevent-forgery-in-maratha-kunbi-certificates-sub-committee-demands-2900-crore-for-obc-ministry-welfare-schemes-1384585</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917031413</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482/amp</t>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/lite/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-tribal-land-lease-policy-chandrashekhar-bawankule-announcement-1361630.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
+          <t>https://navbharatlive.com/maharashtra/chandrapur/minister-chandrashekhar-bawankule-instructed-administration-to-work-seriously-1363447.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/dhananjay-deshmukh-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95-%E0%A4%AE-%E0%A4%82%E0%A4%A1-%E0%A4%AF%E0%A4%B2-%E0%A4%B9%E0%A4%B5-%E0%A4%B9-%E0%A4%A4-%E0%A4%A7%E0%A4%A8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%AE%E0%A5%81%E0%A4%96-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%95%E0%A5%87%E0%A4%B2-%E0%A4%96%E0%A4%82%E0%A4%A4/ar-AA1An2uc?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40193-txt-pune-today-20250918034152</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/send-your-vote-list-rahul-gandhi-minister-bawankule-promise-repay-loan-5-years-1363241.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/lite/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
+          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628/amp</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/now-tribal-lands-will-be-available-on-lease-chandrashekhar-bawankule/</t>
+          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=3&amp;liveblog_last=90890-1757948209</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90863-1757936847</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-mine-owners-are-in-trouble-mining-in-mountains-and-hills-banned-revenue-minister-bawankules-firm-stance/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/pandit-deendayal-upadhyay-employment-fair-organized.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
+          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-accused-of-fake-maratha-kunbi-caste-certificate-documents-manoj-jarange-patil-1494274.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/shivbhojan-thali-the-shivbhojan-thali-of-uddhav-thackerays-era-will-continue-bawankule-clearly-stated/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
+          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shind-10/923721/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%86%E0%A4%A6%E0%A4%BF%E0%A4%B5%E0%A4%BE%E0%A4%B8%E0%A5%80%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%9C%E0%A4%AE%E0%A5%80%E0%A4%A8-%E0%A4%AD%E0%A4%BE%E0%A4%A1%E0%A5%87%E0%A4%A4%E0%A4%A4%E0%A5%8D%E0%A4%A4/118039/</t>
+          <t>https://puneprahar.com/2025/09/imd-weather-update-big-crisis-in-maharashtra-29-districts-on-high-alert-for-rain-today-step-out-of-the-house-only-if-necessary/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B0%E0%A4%BE%E0%A4%9C%E0%A5%8D%E0%A4%AF%E0%A4%AD%E0%A4%B0%E0%A4%BE%E0%A4%A4%E0%A5%80%E0%A4%B2-%E0%A5%A7%E0%A5%A8-%E0%A4%B9%E0%A4%9C%E0%A4%BE%E0%A4%B0-%E0%A5%AC%E0%A5%A6%E0%A5%A6-%E0%A4%B8/118036/</t>
+          <t>https://puneprahar.com/2025/09/croma-launches-new-store-in-kothrud-pune-get-up-to-%E2%82%B930000-cashback-and-free-premium-gifts/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/banjara-reservation-%E0%A4%AC%E0%A4%82%E0%A4%9C-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%87%E0%A4%96%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%A3%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%B9-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%9A-%E0%A4%A8-%E0%A4%82%E0%A4%A6/ar-AA1MArpW</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%B7-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1CXkyZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A8%E0%A4%B5%E0%A4%B0-%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%A4%E0%A5%8D%E0%A4%B8%E0%A4%B5-%E0%A4%A4-%E0%A4%B2-%E0%A4%97%E0%A4%B0%E0%A4%AC-%E0%A4%AB%E0%A4%95%E0%A5%8D%E0%A4%A4-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%A4%E0%A4%AA-%E0%A4%B8-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B9-%E0%A4%82%E0%A4%A6%E0%A5%82-%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A4%A6%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A5%82%E0%A4%AE-%E0%A4%95%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%B9-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1MWJzB</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/amp/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/chhagan-bhujbal-demands-probe-into-fake-obc-certificates/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/news/revenue-ministers-big-announcement-on-the-excavation-of-murum-for-the-repair-of-panand-roads-in-the-state-a-a975/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/aap-chandrapur.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/vijay-wadettiwar-vs-chandrashekhar-bawankule-reservation-gr-wadettiwar-s-elgar-marathi-news-1075795.html</t>
+          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-letest-marathi-news-update-15-sept-2025-maharashtra-politics-ram-satpute-dhananjay-munde-banjara-community-anajali-damania-rohit-pawar-pune-politics-manoj-jarange-patil-chandrashekhar-bawankule-ashish-shelar-uddhav-thackeray-as11</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-local-body-polls-chandrashekhar-bawankule-on-ticket-distribution-public-opinion-to-decide-candidates-amidst-chandrapur-factionalism-1385673</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bes11-mh-bawankule-farmers.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-govt-to-prevent-forgery-in-maratha-kunbi-certificates-sub-committee-demands-2900-crore-for-obc-ministry-welfare-schemes-1384585</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-residents-question-plan-to-start-60-private-property-regn-centres-in-maha/articleshow/124055902.cms</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/maharashtra/vishwa-hindu-parishadno-muslims-allowed-in-garba-marathi-news/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom30-mh-obc-committee-certificates.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/navratri-utsav-only-hindus-allowed-in-garbhas-vishva-hindu-parishad-takes-this-stand/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-gives-rs-40-crore-loan-guarantee-to-sugar-mill-linked-to-ncp-sp-neta-prataprao-dhakne/articleshow/124061371.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/amp/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-tribal-land-lease-policy-chandrashekhar-bawankule-announcement-1361630.html/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
+          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-latest-live-news-updates-20th-september-2025-sharad-pawar-jayant-patil-gopichand-padalkar-bjp-ncp-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-live-news-today-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-government-allows-tribal-farmers-to-lease-land-to-private-companies-1362201.html/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/ncp-sharad-pawar-evm-demo-bawankule-reaction-1356810.html/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/farming-ideas/latest-news-see-what-bhandara-district-farmers-did-to-control-the-khodkid-of-crops-read-in-detail-a-a993/</t>
+          <t>https://www.dainikprabhat.com/wagholi-news-wadebolhai-gram-panchayat-gets-aap-sarkar-seva-kendra/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371/amp</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://www.newsdrum.in/national/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move-10482221</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
+          <t>https://pudhari.news/maharashtra/mumbai/vhp-navratri-garba-entry-hindus-only-ab96</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=3&amp;liveblog_last=90890-1757948209</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom22-mh-tribals-land-lease.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90863-1757936847</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/lite/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/tragic-incident-two-teen-boys-drown-in-pond-while-taking-photos-families-devastated-community-in-shock-latest-marathi-news-yps99</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/buldhana-farmers-threaten-mass-movement-if-government-fails-to-announce-wet-drought-bdk97</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/pune-navratri-festival-inaugurates-this-year-135935585.html</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/big-news-garba-only-for-hindus-vhps-conditions/</t>
+          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/maratha-kunbi-certificates-should-be-issued-only-after-thorough-verification-decision-taken-in-obc-ministry-sub-committee-meeting-05-697489</t>
+          <t>https://divyamarathi.bhaskar.com/national/news/orders-to-sprinkle-cow-urine-on-people-during-garba-in-maharashtra-135974133.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
+          <t>https://www.loksatta.com/maharashtra/dcm-ajit-pawar-on-call-ips-anjana-krishna-controversy-solapur-murum-royalty-case-politics-gkt-96-5380223/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/lite/</t>
+          <t>https://marathi.indiatimes.com/e-paper/trimbakeshwar-womens-pot-protest-against-water-shortage/articleshow/123916850.cms</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
+          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/sports/suryakumar-yadav-team-to-take-to-the-field-against-oman-today-will-the-players-on-the-bench-get-a-chance-sjk95</t>
+          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-action-will-be-taken-against-bogus-documents-decision-of-obc-cabinet-sub-committee-meeting-under-discussion/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chanda-revenue-mitra-chatbot-launch-chandrapur/</t>
+          <t>https://news34.in/2025/09/chandrapur-obc-leaders-statements-2025/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-rss-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1HLd3n?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.newsdrum.in/national/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-10482393</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
+          <t>https://telugu.getlokalapp.com/maharashtra-news/nagpur/ramtek/nagpur-bawankule-s-allegations-on-vadettiwar-s-allegations-15455305</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
+          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom27-mh-tribals-ld-land-lease.amp.html</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/weather/the-rains-will-stop-the-monsoons-return-journey-will-begin-how-do-you-know-when-the-monsoon-will-leave-a-a975/</t>
+          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-latest-live-news-updates-20th-september-2025-sharad-pawar-jayant-patil-gopichand-padalkar-bjp-ncp-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-live-news-today-local-crime-top-headlines</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
+          <t>https://english.bombaysamachar.com/mumbai/vhp-stirs-controversy-with-advisory-for-hindu-only-garba-events-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/vhp-says-only-hindus-allowed-at-garba-events-congress-slams-divisive-agenda-207684</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
+          <t>https://www.newsdrum.in/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2933cr-pending-funds-10470839</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
+          <t>https://chandablast.com/?p=50509</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
+          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://chandablast.com/?p=51003</t>
+          <t>https://www.indiejournal.in/article/sakshep-eci-vote-chori-controversy</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-videovsd-99-5388756/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/maharashtra-news-at-this-time-20-districts-and-81-talukas-will-be-formed-in-the-state/</t>
+          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move-10483282</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom27-mh-tribals-ld-land-lease.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/vhp-navratri-garba-entry-hindus-only-ab96</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/ex-bjp-corporator-arrested-nashik-law-and-order-amid-political-unrest-panchvati-shooting-case-vsd-99-5388883/</t>
+          <t>https://punemirror.com/city/pune/7500-students-take-cleanliness-pledge-in-pune-to-mark-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/nashik-traffic-diversions-announced-navratri-celebrations-kalika-mata-renuka-devi-temples-vsd-99-5388871/lite/</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/gopichand-padalkar-no-apology-statement-ng81</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/global-level-tourist-destination-to-come-up-at-koradi-mou-signed-in-presence-of-cm-sdj87</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/uddhav-thackeray-shiv-sena-restructures-jalgaon-ahead-local-body-elections-new-appointments-vsd-99-5388810/lite/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/amp_articleshow/124004941.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/navratri-new-decision-from-vishwa-hindu-parishad-aadhaar-card-mandatory-to-watch-garba-during-navratri/133217/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/amp/story/india%2Fmaharashtra%2Fvhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/amp_articleshow/124004750.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/amp/story/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>https://divyamarathi.bhaskar.com/national/news/orders-to-sprinkle-cow-urine-on-people-during-garba-in-maharashtra-135974133.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/amit-shah-declares-bokaro-in-jharkhand-maoist-free/articleshow/123916647.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/trimbakeshwar-womens-pot-protest-against-water-shortage/articleshow/123916850.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>https://www.dainikprabhat.com/wagholi-news-wadebolhai-gram-panchayat-gets-aap-sarkar-seva-kendra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-action-will-be-taken-against-bogus-documents-decision-of-obc-cabinet-sub-committee-meeting-under-discussion/</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/politics/a-conspiracy-has-been-hatched-to-defame-laxman-hake-vijay-vadettiwar-claims/133273/</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>https://news34.in/2025/09/chandrapur-obc-leaders-statements-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178604/</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/agriculture/farming-ideas/karnataka-on-the-lines-of-andhra-pradesh-a-a975/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%86%E0%A4%A4-%E0%A4%95-%E0%A4%AF%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%B0-%E0%A4%AE-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A4%A4-%E0%A4%AA-%E0%A4%A3%E0%A4%82%E0%A4%A6-%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%9A%E0%A5%87-%E0%A4%A1-%E0%A4%9C-%E0%A4%9F%E0%A4%B2-%E0%A4%B0%E0%A5%87%E0%A4%95-%E0%A4%B0%E0%A5%8D%E0%A4%A1-%E0%A4%AB-%E0%A4%AF%E0%A4%A6%E0%A5%87-%E0%A4%B5-%E0%A4%9A%E0%A5%82%E0%A4%A8-%E0%A4%86%E0%A4%A8%E0%A4%82%E0%A4%A6%E0%A5%82%E0%A4%A8-%E0%A4%9C-%E0%A4%B2/ar-AA1MvyUA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom38-mh-garba-ld-vhp.amp.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/political-pulse/maratha-quota-fadnavis-govt-catch-22-floodgates-demands-10258572/</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/en-in/news/India/maratha-quota-row-rumblings-in-mahayuti-alliance-chhagan-bhujbal-skips-cabinet-meet/ar-AA1LQ2jJ?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom30-mh-obc-committee-certificates.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-accused-of-fake-maratha-kunbi-caste-certificate-documents-manoj-jarange-patil-1494274.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/amp/story/india%2Fmaharashtra%2Ftribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/en-in/autos/photos/velhe-taluka-in-pune-renamed-after-chhatrapati-shivajis-first-capital-fort-rajgad/ar-AA1KZLQZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>https://chandablast.com/?p=50509</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90839-1757925166</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>https://www.berartimes.com/vidarbha/216594/</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>https://www.indiejournal.in/article/sakshep-eci-vote-chori-controversy</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>https://www.business-standard.com/amp/india-news/himachal-rains-death-toll-rises-to-427-243-rain-related-184-in-accidents-125092000391_1.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/mou-between-maharashtra-government-and-naam-foundation-284511/</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/kunbi-caste-certificate-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%AC-%E0%A4%97%E0%A4%B8-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%82%E0%A4%9A-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A4%96-%E0%A4%B2-%E0%A4%AA%E0%A4%A1%E0%A4%A4-%E0%A4%B3%E0%A4%A3/ar-AA1MHcDS</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/khadgaon-farmer-suicide-case-inquiry-report-submitted-to-collector-mj18</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>https://ratnagirikhabardar.com/news/79889/</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/law-order/3634600-maharashtras-new-lease-law-a-boon-or-bane-for-tribal-farmers</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2933cr-pending-funds-10470839</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>https://www.socialnews.xyz/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha-local-body-polls/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ssubt-fears-rigging-tampering-with-voter-list-in-maha-local-body-polls</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/pune/7500-students-take-cleanliness-pledge-in-pune-to-mark-pm-modis-75th-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/global-level-tourist-destination-to-come-up-at-koradi-mou-signed-in-presence-of-cm-sdj87</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/detail/national/Maharashtra-OBC-panel-orders-strict-scrutiny-of-caste-certificates-clears-Rs-2-933cr-pending-funds/2920779</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/navratri-new-decision-from-vishwa-hindu-parishad-aadhaar-card-mandatory-to-watch-garba-during-navratri/133217/</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>https://www.outlookindia.com/amp/story/national/vhp-says-only-hindus-should-be-allowed-at-garba-sparks-political-row-in-maharashtra</t>
+          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A219"/>
+  <dimension ref="A1:A188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,483 +438,483 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178572/</t>
+          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
+          <t>https://mahasamvad.in/179502/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-video-vsd-99-5388756/</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
+          <t>https://mahasamvad.in/178572/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
+          <t>https://chandablast.com/?p=50932</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/revenue-minister-bawankules-announcement-in-gadchiroli-phm-00-5385317/</t>
+          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-video-vsd-99-5388756/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
+          <t>https://mahasamvad.in/179430/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/politics/new-districts-in-maharashtra-chandrashekhar-bawankule-big-statement-03-698118</t>
+          <t>https://www.loksatta.com/nagpur/revenue-minister-bawankules-announcement-in-gadchiroli-phm-00-5385317/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/government-aims-transform-pune-world-class-infrastructure-chandrashekhar-bawankule-agn97</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece</t>
+          <t>https://puneprahar.com/2025/09/proposal-to-create-20-new-districts-and-81-talukas-in-the-state-information-from-revenue-minister-chandrashekhar-bawankule/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-encroachment-on-farm-roads-to-be-cleared-govt-to-map-such-pathways-says-bawankule/ar-AA1MXpLZ</t>
+          <t>https://www.msn.com/en-in/news/India/state-to-soon-allow-private-entities-to-lease-tribal-lands/ar-AA1MYFKc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1292529</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister/2747478/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1292529</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/headlines/3634796-maharashtras-road-to-prosperity-revamping-farm-access-for-farmers</t>
+          <t>https://www.ptinews.com/story/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move/2934001</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://theprint.in/india/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister/2747478/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
+          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-encroachment-on-farm-roads-to-be-cleared-govt-to-map-such-pathways-says-bawankule/ar-AA1MXpLZ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
+          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
+          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
+          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
+          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178575/</t>
+          <t>https://www.esakal.com/pune/chandrashekhar-bawankule-slams-uddhav-thackeray-says-opposing-reservation-is-wrong-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrashekhar-bawankule-slams-uddhav-thackeray-says-opposing-reservation-is-wrong-politics-pjp78</t>
+          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chief-minister-focus-pune-development-chandrashekhar-bawanakule-sb97</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
+          <t>https://mahasamvad.in/178575/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
+          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
+          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/chandrashekhar-bawankule-says-government-got-proposal-for-20-new-district/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
+          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/chandrashekhar-bawankule-has-instructed-that-certificates-should-not-be-issued-on-basis-of-documents-to-curb-fake-caste-certificates-mvk02</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
+          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://www.esakal.com/mumbai/chandrashekhar-bawankule-has-instructed-that-certificates-should-not-be-issued-on-basis-of-documents-to-curb-fake-caste-certificates-mvk02</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
+          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/chhagan-bhujbal-fake-kunbi-certificates-controversy-obc-meeting-hn97</t>
+          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/22/relief-due-to-gst-reforms-common-people-benefit-from-reduction-in-tax-rates-on-daily-use-items-revenue-ministe.amp.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE/ar-AA1zoITs?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
         </is>
       </c>
     </row>
@@ -928,364 +928,364 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://www.nagpurtoday.in/bawankules-initiative-five-nagpur-pilgrimage-sites-granted-b-category-status/09191501</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/vision-for-pune-transforming-into-indias-top-infrastructure-hub-chandrashekhar-bawankule-pjp78</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
+          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-has-made-murum-mining-royalty-free-1484899.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
+          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
+          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%97-%E0%A4%AF%E0%A4%95%E0%A4%B5-%E0%A4%A1-%E0%A4%AC-%E0%A4%B2%E0%A4%B2%E0%A5%87-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%81%E0%A4%A8%E0%A5%8D%E0%A4%B9-%E0%A4%B5-%E0%A4%A6-%E0%A4%A4-%E0%A4%B8-%E0%A4%AA%E0%A4%A1%E0%A4%B2%E0%A5%87-%E0%A4%9D%E0%A5%87%E0%A4%A1%E0%A4%AA-%E0%A4%86%E0%A4%A3-%E0%A4%AA%E0%A4%82%E0%A4%9A-%E0%A4%AF%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%A4-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%81%E0%A4%95-%E0%A4%82%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%B5-%E0%A4%A6%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A4%95%E0%A5%8D%E0%A4%A4%E0%A4%B5%E0%A5%8D%E0%A4%AF/ar-AA1N0sRo?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917024051</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917024051</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
+          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40193-txt-pune-today-20250918034152</t>
+          <t>https://www.lokmat.com/pune/pune-news-district-collector-ordered-to-prepare-minor-mineral-plan-for-the-district-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
+          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shiv-bhojan-thali-scheme-to-continue-in-maharashtra-with-200-crore-approval-closed-centers-to-reopen-1385628</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l39374-txt-pune-today-20250916120459</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40193-txt-pune-today-20250918034152</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
+          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79258/</t>
+          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-mine-owners-are-in-trouble-mining-in-mountains-and-hills-banned-revenue-minister-bawankules-firm-stance/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
+          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/chandrashekhar-bawankule-praises-new-gst-reform/133431/</t>
+          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79689/</t>
+          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
+          <t>https://ratnagirikhabardar.com/news/79689/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/chhagan-bhujbal-demands-probe-into-fake-obc-certificates/</t>
+          <t>https://lokmat.news18.com/videos/video/vijay-wadettiwar-vs-chandrashekhar-bawankule-reservation-gr-wadettiwar-s-elgar-marathi-news-1075795.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-letest-marathi-news-update-15-sept-2025-maharashtra-politics-ram-satpute-dhananjay-munde-banjara-community-anajali-damania-rohit-pawar-pune-politics-manoj-jarange-patil-chandrashekhar-bawankule-ashish-shelar-uddhav-thackeray-as11</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/aap-chandrapur.html</t>
+          <t>https://marathi.ndtv.com/videos/gautam-adani-sebi-has-dismissed-all-allegations-thanks-to-everyone-who-was-with-us-998035</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-letest-marathi-news-update-15-sept-2025-maharashtra-politics-ram-satpute-dhananjay-munde-banjara-community-anajali-damania-rohit-pawar-pune-politics-manoj-jarange-patil-chandrashekhar-bawankule-ashish-shelar-uddhav-thackeray-as11</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-local-body-polls-chandrashekhar-bawankule-on-ticket-distribution-public-opinion-to-decide-candidates-amidst-chandrapur-factionalism-1385673</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-obc-reservation-maharashtra-govt-to-prevent-forgery-in-maratha-kunbi-certificates-sub-committee-demands-2900-crore-for-obc-ministry-welfare-schemes-1384585</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-tribal-land-lease-policy-chandrashekhar-bawankule-announcement-1361630.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
+          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-tribal-land-lease-policy-chandrashekhar-bawankule-announcement-1361630.html</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/maharashtra-government-allows-tribal-farmers-to-lease-land-to-private-companies-1362201.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
+          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/chandrapur/minister-chandrashekhar-bawankule-instructed-administration-to-work-seriously-1363447.html</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/send-your-vote-list-rahul-gandhi-minister-bawankule-promise-repay-loan-5-years-1363241.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/send-your-vote-list-rahul-gandhi-minister-bawankule-promise-repay-loan-5-years-1363241.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
         </is>
       </c>
     </row>
@@ -1299,665 +1299,448 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=3&amp;liveblog_last=90890-1757948209</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-rain-live-mumbai-pune-nagpur-traffic-local-trains-flood-imd-alert-update-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-breaking-rak-94-5372752/lite/?liveblog_page=2&amp;liveblog_last=90863-1757936847</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/pandit-deendayal-upadhyay-employment-fair-organized.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-accused-of-fake-maratha-kunbi-caste-certificate-documents-manoj-jarange-patil-1494274.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
+          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/desh-videsh/live-update-monsoon-2025-rain-update-maharashtra-rain-update-maharashtra-maharashtra-politics-maharashtra-political-news-breaking-news-mumbai-mumbai-news-cm-devendra-fadnavis-deputy-cm-eknath-shind-10/923721/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/09/imd-weather-update-big-crisis-in-maharashtra-29-districts-on-high-alert-for-rain-today-step-out-of-the-house-only-if-necessary/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/09/croma-launches-new-store-in-kothrud-pune-get-up-to-%E2%82%B930000-cashback-and-free-premium-gifts/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%B7-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1CXkyZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
+          <t>https://ahmednagarlive24.com/maharashtra/maharashtra-news-at-this-time-20-districts-and-81-talukas-will-be-formed-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
+          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bes11-mh-bawankule-farmers.html</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-residents-question-plan-to-start-60-private-property-regn-centres-in-maha/articleshow/124055902.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/pune-navratri-festival-inaugurates-this-year-135935585.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom30-mh-obc-committee-certificates.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/govt-gives-rs-40-crore-loan-guarantee-to-sugar-mill-linked-to-ncp-sp-neta-prataprao-dhakne/articleshow/124061371.cms</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
+          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/ajchya-tajya-batmya-maharashtra-marathi-latest-live-news-updates-20th-september-2025-sharad-pawar-jayant-patil-gopichand-padalkar-bjp-ncp-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-live-news-today-local-crime-top-headlines</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/wagholi-news-wadebolhai-gram-panchayat-gets-aap-sarkar-seva-kendra/</t>
+          <t>https://www.indianwitness.com/news/national/maharashtra-law-lets-tribal-farmers-lease-land-to-priva</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
+          <t>https://www.lokmat.com/agriculture/farming-ideas/announcement-of-a-new-scheme-for-farm-roads-mukhyamantri-baliraja-panand-raste-how-will-the-action-be-taken-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move-10482221</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
+          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/vhp-navratri-garba-entry-hindus-only-ab96</t>
+          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom22-mh-tribals-land-lease.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
+          <t>https://english.bombaysamachar.com/mumbai/vhp-stirs-controversy-with-advisory-for-hindu-only-garba-events-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/pune-navratri-festival-inaugurates-this-year-135935585.html</t>
+          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/national/news/orders-to-sprinkle-cow-urine-on-people-during-garba-in-maharashtra-135974133.html</t>
+          <t>https://www.5dariyanews.com/news/467620-Maharashtra-Govt-Signs-Landmark-MoU-to-Transform-Koradi-into-Eco-Tourism-Hub</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
+          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/dcm-ajit-pawar-on-call-ips-anjana-krishna-controversy-solapur-murum-royalty-case-politics-gkt-96-5380223/</t>
+          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/trimbakeshwar-womens-pot-protest-against-water-shortage/articleshow/123916850.cms</t>
+          <t>https://www.indiejournal.in/article/sakshep-eci-vote-chori-controversy</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/maharashtra-action-will-be-taken-against-bogus-documents-decision-of-obc-cabinet-sub-committee-meeting-under-discussion/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-obc-leaders-statements-2025/</t>
+          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-10482393</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/nagpur/ramtek/nagpur-bawankule-s-allegations-on-vadettiwar-s-allegations-15455305</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom27-mh-tribals-ld-land-lease.html</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/mou-signed-between-mahagenco-and-nmrda-in-the-presence-of-the-chief-minister/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>https://english.bombaysamachar.com/mumbai/vhp-stirs-controversy-with-advisory-for-hindu-only-garba-events-in-maharashtra/</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/maharashtra-obc-panel-orders-strict-scrutiny-of-caste-certificates-clears-rs-2933cr-pending-funds-10470839</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>https://chandablast.com/?p=50509</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>https://www.indiejournal.in/article/sakshep-eci-vote-chori-controversy</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom27-mh-tribals-ld-land-lease.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/pune/7500-students-take-cleanliness-pledge-in-pune-to-mark-pm-modis-75th-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178604/</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/global-level-tourist-destination-to-come-up-at-koradi-mou-signed-in-presence-of-cm-sdj87</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
           <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>https://www.timemaharashtra.com/maharashtra/navratri-new-decision-from-vishwa-hindu-parishad-aadhaar-card-mandatory-to-watch-garba-during-navratri/133217/</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A188"/>
+  <dimension ref="A1:A177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,35 +438,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
+          <t>https://mahasamvad.in/178572/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179502/</t>
+          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178572/</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
@@ -494,28 +494,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179430/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
+          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/revenue-minister-bawankules-announcement-in-gadchiroli-phm-00-5385317/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
+          <t>https://www.loksatta.com/nagpur/revenue-minister-bawankules-announcement-in-gadchiroli-phm-00-5385317/</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/09/proposal-to-create-20-new-districts-and-81-talukas-in-the-state-information-from-revenue-minister-chandrashekhar-bawankule/</t>
+          <t>https://deshonnati.com/officials-should-act-without-condoning-any-wrongdoing/</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/state-to-soon-allow-private-entities-to-lease-tribal-lands/ar-AA1MYFKc</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
@@ -557,35 +557,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
+          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bawankule-backs-organisers--rights--wadettiwar-slams-move/2932800</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1292529</t>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1292529</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move/2934001</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://theprint.in/india/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister/2747478/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister/2747478/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
         </is>
       </c>
     </row>
@@ -599,35 +599,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
+          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-encroachment-on-farm-roads-to-be-cleared-govt-to-map-such-pathways-says-bawankule/ar-AA1MXpLZ</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
+          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
+          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
         </is>
       </c>
     </row>
@@ -648,49 +648,49 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ajit-pawar-downplays-row-with-female-ips-officer/2925297</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
+          <t>https://maharashtratimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
         </is>
       </c>
     </row>
@@ -704,56 +704,56 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178575/</t>
+          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
+          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
         </is>
       </c>
     </row>
@@ -767,980 +767,903 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
+          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
+          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
+          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
+          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
+          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/chandrashekhar-bawankule-has-instructed-that-certificates-should-not-be-issued-on-basis-of-documents-to-curb-fake-caste-certificates-mvk02</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
+          <t>https://sarkarnama.esakal.com/mumbai/chhagan-bhujbal-fake-kunbi-certificates-controversy-obc-meeting-hn97</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
+          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE/ar-AA1zoITs?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%95%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%AC-%E0%A4%B5%E0%A4%A8%E0%A4%95%E0%A5%81%E0%A4%B3%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE-%E0%A4%A0%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8-%E0%A4%AE%E0%A5%81%E0%A4%96%E0%A5%8D%E0%A4%AF%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A0%E0%A4%B0%E0%A4%B5%E0%A4%B2%E0%A4%82%E0%A4%AF-%E0%A4%95/ar-AA1NcvqY</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
+          <t>https://www.lokmat.com/pune/pune-news-district-collector-ordered-to-prepare-minor-mineral-plan-for-the-district-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
+          <t>https://www.nagpurtoday.in/bawankules-initiative-five-nagpur-pilgrimage-sites-granted-b-category-status/09191501</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankules-initiative-five-nagpur-pilgrimage-sites-granted-b-category-status/09191501</t>
+          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
+          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/revenue-minister-chandrashekhar-bawankule-has-made-murum-mining-royalty-free-1484899.html</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
+          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917024051</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
+          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917024051</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
+          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
+          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-district-collector-ordered-to-prepare-minor-mineral-plan-for-the-district-a-a1008/</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40193-txt-pune-today-20250918034152</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
+          <t>https://news18marathi.com/agriculture/revenue-minister-bawankule-has-given-information-about-the-documents-in-the-tukdebandi-1482532.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l39374-txt-pune-today-20250916120459</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40193-txt-pune-today-20250918034152</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
+          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
+          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://ratnagirikhabardar.com/news/79689/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/private-companies-can-also-lease-wasteland-tribal-land-125092100014_1.html</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-letest-marathi-news-update-15-sept-2025-maharashtra-politics-ram-satpute-dhananjay-munde-banjara-community-anajali-damania-rohit-pawar-pune-politics-manoj-jarange-patil-chandrashekhar-bawankule-ashish-shelar-uddhav-thackeray-as11</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79689/</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
+          <t>https://www.khabar24.tv/2025/09/25/chandrashekhar-bawankule-wrote-a-thank-you-letter-to-pm-modi-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/vijay-wadettiwar-vs-chandrashekhar-bawankule-reservation-gr-wadettiwar-s-elgar-marathi-news-1075795.html</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/maharashtra-government-allows-tribal-farmers-to-lease-land-to-private-companies-1362201.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-letest-marathi-news-update-15-sept-2025-maharashtra-politics-ram-satpute-dhananjay-munde-banjara-community-anajali-damania-rohit-pawar-pune-politics-manoj-jarange-patil-chandrashekhar-bawankule-ashish-shelar-uddhav-thackeray-as11</t>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/gautam-adani-sebi-has-dismissed-all-allegations-thanks-to-everyone-who-was-with-us-998035</t>
+          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/send-your-vote-list-rahul-gandhi-minister-bawankule-promise-repay-loan-5-years-1363241.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-tribal-land-lease-policy-chandrashekhar-bawankule-announcement-1361630.html</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://vsrsnews.in/pimpri-chinchwad/pune-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/maharashtra-government-allows-tribal-farmers-to-lease-land-to-private-companies-1362201.html</t>
+          <t>https://www.lokmat.com/editorial/editorial-special-articles-then-a-new-khichdi-will-be-cooked-in-maharashtra-if-there-is-too-much-pressure-from-above-to-live-together-rebellion-will-break-out-a-a285-c941/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/send-your-vote-list-rahul-gandhi-minister-bawankule-promise-repay-loan-5-years-1363241.html</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/revenue-departments-lok-adalat-campaign-for-farmers-to-start-from-september-17-1480838.html</t>
+          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
+          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
+          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
+          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/maharashtra/maharashtra-news-at-this-time-20-districts-and-81-talukas-will-be-formed-in-the-state/</t>
+          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
+          <t>https://divyamarathi.bhaskar.com/national/news/orders-to-sprinkle-cow-urine-on-people-during-garba-in-maharashtra-135974133.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
+          <t>https://maharashtratimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
+          <t>https://thelivenagpur.com/2025/09/15/guardian-minister-reviews-preparations-for-deekshabhoomi-and-navratri/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/pune-navratri-festival-inaugurates-this-year-135935585.html</t>
+          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://www.lokmat.com/agriculture/farming-ideas/announcement-of-a-new-scheme-for-farm-roads-mukhyamantri-baliraja-panand-raste-how-will-the-action-be-taken-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/sinnar-17-25-percent-increase-in-water-bill-sima-organization-strongly-oppose/articleshow/123916891.cms</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://indianexpress.com/article/political-pulse/maratha-quota-fadnavis-govt-catch-22-floodgates-demands-10258572/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
+          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
+          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.indianwitness.com/news/national/maharashtra-law-lets-tribal-farmers-lease-land-to-priva</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/farming-ideas/announcement-of-a-new-scheme-for-farm-roads-mukhyamantri-baliraja-panand-raste-how-will-the-action-be-taken-a-a975/</t>
+          <t>https://english.bombaysamachar.com/mumbai/vhp-stirs-controversy-with-advisory-for-hindu-only-garba-events-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
+          <t>https://www.5dariyanews.com/news/467620-Maharashtra-Govt-Signs-Landmark-MoU-to-Transform-Koradi-into-Eco-Tourism-Hub</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
+          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://english.bombaysamachar.com/mumbai/vhp-stirs-controversy-with-advisory-for-hindu-only-garba-events-in-maharashtra/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
+          <t>https://mahasamvad.in/178604/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467620-Maharashtra-Govt-Signs-Landmark-MoU-to-Transform-Koradi-into-Eco-Tourism-Hub</t>
+          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
+          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>https://www.indiejournal.in/article/sakshep-eci-vote-chori-controversy</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bom27-mh-tribals-ld-land-lease.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178604/</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
+          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrashekhar Bawankule/extracted_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A177"/>
+  <dimension ref="A1:A170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,42 +438,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178572/</t>
+          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrashekhar-bawankule-interacted-with-reporters-at-the-district-collectors-office-phm-00-5387245/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-plans-law-to-lease-tribal-barren-land-to-private-companies</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://chandablast.com/?p=50932</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
@@ -487,14 +487,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
@@ -515,182 +515,182 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/revenue-minister-bawankules-announcement-in-gadchiroli-phm-00-5385317/</t>
+          <t>https://mpbreakingnews.in/marathi/politics/new-districts-in-maharashtra-chandrashekhar-bawankule-big-statement-03-698118</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/officials-should-act-without-condoning-any-wrongdoing/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece</t>
+          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1292529</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/vhp-issues--hindus-only--diktat-for-garba;-bawankule-backs-organisers--rights--wadettiwar-slams-move/2932800</t>
+          <t>https://www.ptinews.com/editor-detail/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities;-govt-to-bring-law--minister/2932661</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1292529</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister/2747478/</t>
+          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes34-mh-ajit-soil-royalty.html</t>
+          <t>https://www.indianwitness.com/news/national/better-roads-bigger-profits-maharashtras-new-scheme-for</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
+          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
+          <t>https://www.ptinews.com/story/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move/2934001</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
+          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
+          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://maharashtratimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/bjp-leader-chandrashekhar-bawankule-ridiculed-the-ncps-resolution-declarations-only-to-stop-workers-from-leaving-the-party-rm96-rc70</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
         </is>
       </c>
     </row>
@@ -732,112 +732,112 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
+          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
+          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
+          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
+          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
+          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/nagpur-news-harshvardhan-sapkal-should-check-his-height-before-talking-about-modi-bawankule-997380.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/chandrashekhar-bawankule-gives-important-instructions-to-officers-chhagan-bhujbal-on-maratha-kunbi-certificate-distribution-and-obc-reservation-maharashtra-news-mhs25091605134</t>
+          <t>https://marathi.ndtv.com/videos/bawankule-no-tickets-for-those-who-follow-leaders-bawankule-warns-997430</t>
         </is>
       </c>
     </row>
@@ -851,817 +851,768 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/chhagan-bhujbal-fake-kunbi-certificates-controversy-obc-meeting-hn97</t>
+          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
+          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
+          <t>https://www.lokmat.com/pune/pune-news-district-collector-ordered-to-prepare-minor-mineral-plan-for-the-district-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ajit-pawar-ips-anjana-krishna-dispute-murum-excavation-benefits-41000-villages-maharashtra-dk88</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-district-collector-ordered-to-prepare-minor-mineral-plan-for-the-district-a-a1008/</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
+          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/maharashtra-obc-sub-committee-big-decision-on-kunbi-certificate-distribution-to-maratha-community/articleshow/123921757.cms</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/bawankules-initiative-five-nagpur-pilgrimage-sites-granted-b-category-status/09191501</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
+          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917024051</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
+          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
+          <t>https://www.saamana.com/shiv-bhojan-thali-started-by-uddhav-thackeray-gets-200-crore-fund-by-government/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
+          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
+          <t>https://www.lokmat.com/agriculture/farming-ideas/announcement-of-a-new-scheme-for-farm-roads-mukhyamantri-baliraja-panand-raste-how-will-the-action-be-taken-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
+          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917024051</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chagan-bhujbal-obc-reservation-demands-135934860.html</t>
+          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
+          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-shivbhojan-thali-scheme-to-continue-minister-bawankule-announces-200-crore-approval-for-maharashtra-s-affordable-meal-program-1385482</t>
+          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
+          <t>https://ratnagirikhabardar.com/news/79689/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://lokmat.news18.com/videos/video/vijay-wadettiwar-vs-chandrashekhar-bawankule-reservation-gr-wadettiwar-s-elgar-marathi-news-1075795.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40193-txt-pune-today-20250918034152</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/agriculture/revenue-minister-bawankule-has-given-information-about-the-documents-in-the-tukdebandi-1482532.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/maharashtra-government-allows-tribal-farmers-to-lease-land-to-private-companies-1362201.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/as-many-as-20-new-districts-and-81-talukas-have-been-created-in-the-state/</t>
+          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/send-your-vote-list-rahul-gandhi-minister-bawankule-promise-repay-loan-5-years-1363241.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79689/</t>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-letest-marathi-news-update-15-sept-2025-maharashtra-politics-ram-satpute-dhananjay-munde-banjara-community-anajali-damania-rohit-pawar-pune-politics-manoj-jarange-patil-chandrashekhar-bawankule-ashish-shelar-uddhav-thackeray-as11</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
+          <t>https://www.lokmat.com/editorial/editorial-special-articles-then-a-new-khichdi-will-be-cooked-in-maharashtra-if-there-is-too-much-pressure-from-above-to-live-together-rebellion-will-break-out-a-a285-c941/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/25/chandrashekhar-bawankule-wrote-a-thank-you-letter-to-pm-modi-khabar-24-express/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/maharashtra-government-allows-tribal-farmers-to-lease-land-to-private-companies-1362201.html</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/send-your-vote-list-rahul-gandhi-minister-bawankule-promise-repay-loan-5-years-1363241.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/editorial/editorial-special-articles-then-a-new-khichdi-will-be-cooked-in-maharashtra-if-there-is-too-much-pressure-from-above-to-live-together-rebellion-will-break-out-a-a285-c941/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
+          <t>https://indianexpress.com/article/political-pulse/maratha-quota-fadnavis-govt-catch-22-floodgates-demands-10258572/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
+          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/business/3634504-empowering-maharashtras-tribal-farmers-leasing-land-for-agriculture-and-mining</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
+          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
+          <t>https://www.nagpurtoday.in/burglary-in-nagpurs-wathoda-cash-along-with-jewellery-worth-over-rs-6-lakhs-looted/09221724</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
+          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
+          <t>https://www.business-standard.com/india-news/punjab-records-27-stubble-burning-cases-as-govt-boosts-awareness-drive-125092000441_1.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
+          <t>https://civicmirror.in/maharashtra/1100-services-will-be-digitized-under-the-service-guarantee-act-by-may-1st-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
+          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/national/news/orders-to-sprinkle-cow-urine-on-people-during-garba-in-maharashtra-135974133.html</t>
+          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-heavy-rain-traffic-disrupted-and-normal-life-affected-imd-issues-alert-for-next-24-hour/articleshow/123900789.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/09/15/guardian-minister-reviews-preparations-for-deekshabhoomi-and-navratri/</t>
+          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
+          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
+          <t>https://www.etvbharat.com/mr/!videos/vanjari-samaj-leader-balasaheb-sanap-demends-reservation-for-vanjari-in-st-as-per-hyderabad-gazette-watch-video-mhs25091903949</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/farming-ideas/announcement-of-a-new-scheme-for-farm-roads-mukhyamantri-baliraja-panand-raste-how-will-the-action-be-taken-a-a975/</t>
+          <t>https://english.bombaysamachar.com/mumbai/vhp-stirs-controversy-with-advisory-for-hindu-only-garba-events-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/maratha-quota-fadnavis-govt-catch-22-floodgates-demands-10258572/</t>
+          <t>https://www.5dariyanews.com/news/467620-Maharashtra-Govt-Signs-Landmark-MoU-to-Transform-Koradi-into-Eco-Tourism-Hub</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
+          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
+          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://punemirror.com/city/pune/7500-students-take-cleanliness-pledge-in-pune-to-mark-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://english.bombaysamachar.com/mumbai/vhp-stirs-controversy-with-advisory-for-hindu-only-garba-events-in-maharashtra/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467620-Maharashtra-Govt-Signs-Landmark-MoU-to-Transform-Koradi-into-Eco-Tourism-Hub</t>
+          <t>https://www.lokmat.com/nagpur/five-pilgrimage-sites-in-nagpur-district-get-b-class-status-a-a382-c719/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
+          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178604/</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
         <is>
           <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
         </is>

--- a/Output/Chandrashekhar Bawankule/extracted_links.xlsx
+++ b/Output/Chandrashekhar Bawankule/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A170"/>
+  <dimension ref="A1:A161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
+          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
         </is>
       </c>
     </row>
@@ -459,112 +459,112 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrashekhar-bawankule-revenue-minister-u-turn-on-his-statement-over-giving-tribal-land-on-lease-to-non-tribals-gadchiroli-maharashtra-politics-marathi-news-1385418</t>
+          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/revenue-servant-strike-eighth-day-government-not-even-a-simple-acknowledgement-protesters-warn-the-government-nagpur-news-maharashtra-marathi-news-1385371</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-tribal-farmers-land-leasing-income-boost</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/bjp-ticket-distribution-policy-local-body-elections-public-support-decide-candidates-chandrashekhar-bawankule-warn-video-vsd-99-5388756/</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/gadchiroli-revenue-minister-bawankules-announcement-phm-00-5385383/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/navratri-garba-only-for-hindus-check-aadhaar-of-participants-says-vhp-bawankule-comment-1385439</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/land-measurement-mandatory-for-registration-maharashtra-revenue-bawankule-pune-print-news-ocd-94-5385238/</t>
+          <t>https://mpbreakingnews.in/marathi/politics/new-districts-in-maharashtra-chandrashekhar-bawankule-big-statement-03-698118</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-live-blog-updates-19-september-2025-farmer-flood-rain-maharashtra-weather-maharashtra-politics-devendra-fadnavismumbai-rains-1385110</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/politics/new-districts-in-maharashtra-chandrashekhar-bawankule-big-statement-03-698118</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/sena-ubt-criticises-govt-over-match-bawankule-hits-back/articleshow/123887314.cms</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-soon-allow-private-entities-to-lease-tribal-lands-101758396296809.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/tribals-in-maharashtra-can-now-lease-barren-land-to-private-entities-govt-to-bring-law-minister-3737045</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/20/bes11-mh-bawankule-farmers.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
+          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.daijiworld.com/news/newsDisplay?newsID=1292529</t>
+          <t>https://www.indianwitness.com/news/crime/better-roads-bigger-profits-maharashtras-new-scheme-for</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities;-govt-to-bring-law--minister/2932661</t>
+          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
         </is>
       </c>
     </row>
@@ -578,119 +578,119 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-7500-students-take-cleanliness-oath-at-pm-narendra-modis-birthday-event-attended-by-maharashtra-minister-chandrashekhar-bawankule</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.indianwitness.com/news/national/better-roads-bigger-profits-maharashtras-new-scheme-for</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/farmers-in-tribal-areas-can-lease-land-to-private-parties-bawankule/articleshow/124004941.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
+          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/vhp-issues-hindus-only-diktat-for-garba-bjp-minister-backs-organisers-rights-cong-slams-move/2934001</t>
+          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/vhp-issues-hindus-only-diktat-for-garba-bawankule-backs-organisers-rights-wadettiwar-slams-move/articleshow/124014945.cms</t>
+          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-government-approves-land-for-expansion-of-11-villages-in-nashik-district</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bawankule-criticises-ubt-defends-right-to-use-balasaheb-photo/articleshow/123907925.cms</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/guardian-minister-bawankule-secures-b-category-status-for-five-major-pilgrimage-sites-in-nagpur-district/09191502</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/chandrashekhar-bawankule-big-statement-on-maharashtra-new-20-districts-81-talukas-dk88</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/tribal-farmers-in-maharashtra-can-now-lease-land-to-private-entities-govt-to-bring-law-minister-10482095</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/new-nagpur-project-farmers-provide-proof-about-no-rr-rate-change-in-10-yrs/articleshow/124052183.cms</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/maharashtra-proposal-to-create-20-new-districts-81-talukas-process-chandrashekhar-bawankule-revenue-minister-news-1386089</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/bjp-leader-chandrashekhar-bawankule-ridiculed-the-ncps-resolution-declarations-only-to-stop-workers-from-leaving-the-party-rm96-rc70</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/e-paper/chandrashekhar-bawankules-important-instructions-for-water-resource-conservation-in-nagpur/articleshow/123916999.cms</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/chandrashekhar-bawankule-statement-on-banjara-reservation-nagpur-as80</t>
+          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/minister-chandrashekhar-bawankule-gives-important-instructions-to-officers-about-maratha-kunbi-certificate-distribution/articleshow/123922415.cms</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-navratri-festival-2025-inauguration-chandrashekhar-bawankule-sb97</t>
+          <t>https://www.esakal.com/mumbai/chandrashekhar-bawankule-has-instructed-that-certificates-should-not-be-issued-on-basis-of-documents-to-curb-fake-caste-certificates-mvk02</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/bjp-leader-chandrashekhar-bawankule-ridiculed-the-ncps-resolution-declarations-only-to-stop-workers-from-leaving-the-party-rm96-rc70</t>
+          <t>https://www.loksatta.com/maharashtra/chandrashekhar-bawankule-on-obc-sub-committee-meeting-and-obc-maratha-kunbi-certificate-politics-gkt-96-5376634/</t>
         </is>
       </c>
     </row>
@@ -704,98 +704,98 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-chandrashekhar-bawankule-order-minor-mineral-plan-of-each-district-in-the-state-pune-print-news-asj-82-5381503/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/revenue-minister-bawankule-statement-tukade-bandi-about-municipal-corporation-municipal-council-and-municipal-panchayat-pune-print-news-asj-82-5381397/</t>
+          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/guardian-minister-chandrashekhar-bawankule-thanks-govt-for-upgrading-nagpurs-religious-sites-sdj87</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/state-approves-land-in-shirdi-for-ib-officers-office-home-bawankule-chaired-meeting-sud-02-5388265/</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/obc-reservation-in-spotlight-vijay-wadettiwar-and-chandrashekhar-bavanukule-address-urgent-issues-sdj87</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
+          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/bawankule-counter-attack-on-vadettivar-politics-sk95</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/chandrashekhar-bawankule-obc-subcommittee-meeting-strict-verification-for-maratha-kunbi-caste-certificates-to-prevent-fake-documents-in-maharashtra-om0906</t>
+          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/gadchiroli/revenue-minister-chandrashekhar-bawankule-announces-that-tribal-lands-can-be-given-on-lease/articleshow/124010200.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/chandrashekhar-bawankule-local-body-elections-ticket-distribution-bjp-strategy-india-rm82-rc70</t>
+          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/gadchiroli/gopeechand-padlkar-statement-wrong-chandrashekhar-bavankule-as80</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrashekhar-bawankule-comment-on-statue-of-late-meenatai-thackeray-issue-pune-print-news-asj-82-5381241/</t>
+          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chandrashekhar-bawankule-criticizes-sharad-pawar-no-role-for-community-welfare-dc95</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/chandrashekhar-bawankule-criticizes-sharad-pawar-maratha-obc-upsamiti-135950317.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/gadchiroli/gadchiroli-non-tribals-will-able-to-take-tribal-lands-on-lease-revenue-minister-chandrashekhar-bawankule-marathi-news-1385320</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
         </is>
       </c>
     </row>
@@ -809,21 +809,21 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-may-get-20-new-districts-and-81-talukas-proposal-submitted-to-government-awaiting-census-report-says-chandrashekhar-bawankule-bbj88</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
+          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/obc-upsamiti-meeting-chandrashekhar-bawankule-chhagan-bhujbal-opposed-flaw-evidence-to-kunbi-certificates-1384586</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-plans-20-new-districts-and-81-talukas-revenue-minister-bawankule-mj18</t>
         </is>
       </c>
     </row>
@@ -844,777 +844,714 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/maharashtra-regulations-will-come-within-fifteen-days-after-scrapping-tukda-ban-information-from-revenue-minister-aau85</t>
+          <t>https://sarkarnama.esakal.com/mumbai/chhagan-bhujbal-fake-kunbi-certificates-controversy-obc-meeting-hn97</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/15/bjp-nagpur-chandrashekhar-bawankule-2025-panchayat-to-parliament-election-strategy-.html</t>
+          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-private-land-survey-agencies-mandatory-registration-ac90</t>
+          <t>https://www.lokmat.com/pune/pune-news-district-collector-ordered-to-prepare-minor-mineral-plan-for-the-district-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/pune-navratri-mahotsav-begins-11-days-of-divine-art-culture-amp17</t>
+          <t>https://pudhari.news/maharashtra/mumbai/shiv-bhojan-thali-scheme-maharashtra-continues-ab96</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/chandrashekhar-bawankule-orders-deep-verification-of-bogus-kunbi-caste-certificates-vvg94</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishesh/nagpur-zilla-parishad-president-nisha-sawarkar-bjp-tekchand-sawarkar-mla-hn97-rc70</t>
+          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-district-collector-ordered-to-prepare-minor-mineral-plan-for-the-district-a-a1008/</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/news/tukadebandi-revenue-minister-gave-this-important-news-regarding-regularization-of-tukadebandi-documents-a-a975/</t>
+          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-chandrashekhar-bawankule-on-local-body-elections-tickets-via-internal-survey-public-opinion-to-decide-not-loyalty-to-leaders-amid-chandrapur-groupism-1385779</t>
+          <t>https://pudhari.news/maharashtra/mumbai/kunbi-bogus-certificates-deep-verification-dc95</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/gadchiroli/houses-built-by-swallowing-tribal-forest-lands-sit-to-investigate-rs-2000-crore-plot-scam-a-a1000/</t>
+          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-20-september-2025-latest-marathi-political-news-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-election-commission-mumbai-pune-chhagan-bhujbal-ncp-bjp-local-body-elections</t>
+          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/16/yogesh-kumbhejkar-seva-pandharvada.html</t>
+          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/videos/chandrashekhar-bawankule-interview-sakal-revenue-minister-maharashtra-issues-kr13</t>
+          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maharashtra-to-make-1100-government-services-online-by-may-cm-fadnavis-mj18</t>
+          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-digital-services-initiative-1100-online-schemes-ac90</t>
+          <t>https://www.lokmat.com/pune/pune-news-if-the-revenue-department-improves-the-entire-state-will-improve-hopes-chief-minister-devendra-fadnavis-suggests-making-revenue-records-online-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-will-take-the-right-decision-without-doing-injustice-to-kalus-farmers-bawankule-a-a1008/</t>
+          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/81-talukas-to-be-created-in-maharashtra-along-with-20-new-districts-marathi-news-1485490.html</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l40086-txt-pune-today-20250917024051</t>
+          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/nagpur/while-creating-a-new-nagpur-every-farmer-will-get-compensation-for-their-land-as-per-the-land-acquisition-act-revenue-minister-claims-a-a382-c1000/</t>
+          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/shiv-bhojan-thali-started-by-uddhav-thackeray-gets-200-crore-fund-by-government/</t>
+          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/fake-obc-certificates-exposed-by-chhagan-bhujbal-ocd-94-5377198/</t>
+          <t>https://lokmat.news18.com/videos/video/vijay-wadettiwar-vs-chandrashekhar-bawankule-reservation-gr-wadettiwar-s-elgar-marathi-news-1075795.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/agriculture/farming-ideas/announcement-of-a-new-scheme-for-farm-roads-mukhyamantri-baliraja-panand-raste-how-will-the-action-be-taken-a-a975/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/ladki-bahin-yojana-e-kyc-verification-mandatory-for-all-beneficiary-at-ladakibahin-maharashtra-gov-in-article-152850258</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/sharadiya-navratri-ritual-worship-of-guardian-minister-chandrashekhar-bawankule-at-koradi-mata-temple/09221722</t>
+          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.adharnewsnetwork.com/2025/09/chandrashekhar-bawankule.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/pakistani-flag-wavers-should-not-teach-us-patriotism-bawankule-attack-on-uddhav-thackeray/09151415</t>
+          <t>https://navbharatlive.com/maharashtra/chandrapur/minister-chandrashekhar-bawankule-instructed-administration-to-work-seriously-1363447.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/no-registration-without-survey-big-decision-of-revenue-department-land-survey-mandatory-before-deed-registration-no-changes-without-registration/</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/obc-sub-committees-decision-thorough-verification-of-kunbi-bogus-certificates/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-tribal-land-lease-policy-chandrashekhar-bawankule-announcement-1361630.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-exemption-from-the-fragmentation-law-sale-of-one-or-two-gunthas-is-now-possible-know-when-the-implementation-will-start/</t>
+          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-news-development-updates/</t>
+          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79689/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.net/Encyc/2025/9/17/devendra-fadnavis-seva-pandharwada.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/vijay-wadettiwar-vs-chandrashekhar-bawankule-reservation-gr-wadettiwar-s-elgar-marathi-news-1075795.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/maha-govt-to-allow-tribal-farmers-to-lease-land-to-private-firms-minister-125092000372_1.html</t>
+          <t>https://www.lokmat.com/editorial/editorial-special-articles-then-a-new-khichdi-will-be-cooked-in-maharashtra-if-there-is-too-much-pressure-from-above-to-live-together-rebellion-will-break-out-a-a285-c941/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/rs500cr-govt-land-grabbed-in-gadchiroli-with-fake-papers-minister/articleshow/124004750.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/political-leaders-spar-over-vhp-advisory-banning-non-hindus-in-garba-events/article70074549.ece</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/chandrashekhar-bawankule-said-vadettiwar-is-practicing-obc-politics-but-bhujbal-isnt-1189531</t>
+          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-bawankule-says-private-companies-also-lease-barren-tribal-land-cm-fadnavis-government-enact-law-2025-09-20</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/maharashtra-government-allows-tribal-farmers-to-lease-land-to-private-companies-1362201.html</t>
+          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/chandrapur/allay-fears-about-obc-reservations-memorandum-submitted-to-minister-bawankule-1363415.html</t>
+          <t>https://www.indianwitness.com/amp/news/crime/better-roads-bigger-profits-maharashtras-new-scheme-for</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/send-your-vote-list-rahul-gandhi-minister-bawankule-promise-repay-loan-5-years-1363241.html</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/09/17/chandrashekhar-bawankule-writes-emotional-letter-to-pm-modi-on-his-birthday-a-big-message-to-the-nation-khabar-24-express/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-udhav-thackeray-raj-thackeray-cm-devendra-fadnavis-sharad-pawar-ncp-obc-reservation-rain-update-saturday-20-september-2025-1496545.html</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/flood-news-ashti.html</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-state-new-district-and-taluka-formation-the-map-of-maharashtra-will-change-81-new-talukas-and-20-districts-will-be-created-in-maharashtra/940852</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chairman-of-maharashtra-legislative-council-statement-on-ram-shinde-marathwada-backwardness-pune-print-news-zws-70-5381328/</t>
+          <t>https://www.tarunbharat.net/Encyc/2025/9/16/crime-news-maulana-arrested.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/indian-railways-made-in-india-technology-locomotive-in-train-engine-pune-print-news-css-98-5381428/</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/vhp-says-only-hindus-allowed-at-garba-events-congress-slams-divisive-agenda-207684</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
+          <t>https://indianexpress.com/article/political-pulse/maratha-quota-fadnavis-govt-catch-22-floodgates-demands-10258572/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/editorial/editorial-special-articles-then-a-new-khichdi-will-be-cooked-in-maharashtra-if-there-is-too-much-pressure-from-above-to-live-together-rebellion-will-break-out-a-a285-c941/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-22-september-2025-latest-marathi-political-news-maratha-manoj-jarange-patil-obc-reservation-mahayuti-devendra-fadnavis-uddhav-thackeray-ajit-pawar-pune-visit-eknath-shinde-ncp-mns-shivsena-ubt-rahul-gandhi-eci-mumbai-chhagan-bhujbal-local-body-elections</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/maharashtra-congress-leaders-in-maratha-reservation-protest-nana-patole-harshvardhan-patil-vijay-wadettiwar-turn-away-from-maratha-reservation-protest-manoj-jarange-patil-maharashtra-politics-mm76</t>
+          <t>https://www.freepressjournal.in/entertainment/ajey-the-untold-story-of-a-yogi-review-anant-vijay-joshi-wins-over-with-his-sincere-attempt</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/20/maharashtra-govt-to-enact-law-to-enable-tribal-farmers-to-lease-land-to-private-entities</t>
+          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/enjoy-shikara-rides-in-koradi-soon-nmrda-mahagenco-sign-mou/articleshow/123928862.cms</t>
+          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/nagpur-officials-review-preparations-for-dhammachakra-pravartan-din/09161920</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-rain-manoj-jarange-chhagan-bhujbal-obc-reservation-devendra-fadnavis-tuesday-16-september-2025-1493374.html</t>
+          <t>https://www.freepressjournal.in/entertainment/bigg-boss-19-contestants-fees-gaurav-khanna-earns-175-lakh-per-week-know-how-much-amaal-mallik-kunickaa-sadanand-others-charged</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-marathi-latest-live-news-updates-19th-september-2025-ajchya-tajya-batmya-mumbai-thane-weather-rain-update-nagpur-pune-nashik-weather-forecast-rain-update-maratha-obc-aarkashan-clash-maharashtra-devendra-fadanvis-eknath-shinde-ajit-pawar-sharad-pawar-raj-thackeray-uddhav-thackeray-live-news-today-local-crime-top-headlines</t>
+          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-news-case-registered-against-teacher-beating-girl-student-over-reason-of-refuse-to-clean-garbage/articleshow/123926192.cms</t>
+          <t>https://pudhari.news/maharashtra/mumbai/gopichand-padalkar-no-apology-statement-ng81</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-sudhir-khandare-dies-in-bathroom-after-allegedly-hit-by-tap-police-solved-murder-mystery-nabs-family/articleshow/123933510.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/maratha-quota-fadnavis-govt-catch-22-floodgates-demands-10258572/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
+          <t>https://www.nagpurtoday.in/burglary-in-nagpurs-wathoda-cash-along-with-jewellery-worth-over-rs-6-lakhs-looted/09221724</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-sub-committee-on-obc-issues-cracks-down-on-bogus-kunbi-certificates-approves-fund-release-and-welfare-measures</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/for-hindu-only-garba-vhp-sets-entry-norms-check-aadhaar-apply-tilak-101758363132840.html</t>
+          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.siasat.com/maharashtra-vhp-issues-diktat-for-garba-entry-based-on-aadhaar-details-3273836/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/for-hindu-only-garba-vhp-sets-entry-rules-aadhaar-tilak-required-7866187.html</t>
+          <t>https://www.navarashtra.com/automobile/how-to-increase-electric-car-range-which-mistakes-should-be-avoided-991242.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-vhp-advises-only-hindus-should-attend-garba-suggests-aadhaar-verification</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/service-fortnight-to-be-implemented-on-the-occasion-of-the-birthdays-of-mahatma-gandhi-and-narendra-modi-amy-95-5374888/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://pudhari.news/national/vishwa-hindu-parishad-wants-garba-events-to-be-exclusive-to-hindus-sets-entry-norms-nl76</t>
+          <t>https://www.indianwitness.com/amp/news/news/maharashtra-law-lets-tribal-farmers-lease-land-to-priva</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/09/chandrapur-bjp-internal-conflict-2026/</t>
+          <t>https://www.businessworld.in/article/maharashtra-allows-tribal-farmers-to-lease-barren-land-to-firms-572455</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-minister-chhagan-bhujbal-demands-verification-of-obc-certificates-issued-to-maratha-community-23594340</t>
+          <t>https://www.business-standard.com/india-news/punjab-records-27-stubble-burning-cases-as-govt-boosts-awareness-drive-125092000441_1.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
+          <t>https://www.lokmat.com/agriculture/farming-ideas/announcement-of-a-new-scheme-for-farm-roads-mukhyamantri-baliraja-panand-raste-how-will-the-action-be-taken-a-a975/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/jsym-to-host-amrit-mahotsavi-international-yoga-convention-in-nagpur-in-november/articleshow/124005000.cms</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/17/state-plans-ecotourism-project-at-koradi.html</t>
+          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/obc-activists-wave-black-flags-during-cms-speech-2-attempt-self-immolation-near-ajit-pawars-convoy/articleshow/123952613.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/vhps-hindus-only-diktat-for-garba-bjp-leader-backs-organisers-rights-oppn-slams-move-3737006</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/survey-of-654-rural-roads-completed-in-nagpur-gramin-taluka-maps-available-for-citizens-mj18</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/burglary-in-nagpurs-wathoda-cash-along-with-jewellery-worth-over-rs-6-lakhs-looted/09221724</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-has-received-no-complaint-of-denial-of-kunbi-certificate-to-eligible-candidates-cm/articleshow/123954996.cms</t>
+          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/govt-to-fast-track-land-ownership-rights-for-bengali-families-in-gadchiroli/articleshow/124004837.cms</t>
+          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://mumbaimirror.indiatimes.com/mumbai/unveiled-uniform-rules-for-hoardings-on-government-land/articleshow/123907327.html</t>
+          <t>https://www.etvbharat.com/mr/!videos/vanjari-samaj-leader-balasaheb-sanap-demends-reservation-for-vanjari-in-st-as-per-hyderabad-gazette-watch-video-mhs25091903949</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-on-remark-on-maharashtra-revenue-department-pune-print-news-zws-70-5381326/</t>
+          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/punjab-records-27-stubble-burning-cases-as-govt-boosts-awareness-drive-125092000441_1.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/banjara-community-holds-two-big-rallies-munde-says-form-panel-to-grant-them-st-status-101757963085577.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/1100-services-will-be-digitized-under-the-service-guarantee-act-by-may-1st-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.tv9marathi.com/videos/chhagan-bhujbal-accused-of-fake-maratha-kunbi-caste-certificate-documents-manoj-jarange-patil-1494274.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/ahilyanagar/matoshree-gram-samruddhi-39-villages-43-km-farm-roads-approval-sb97</t>
+          <t>https://www.freepressjournal.in/entertainment/emmy-awards-2025-fk-ice-and-free-palestine-hacks-actress-hannah-einbinder-speech-goes-viral-watch-video</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/bori-budruk-was-the-first-to-give-the-code-number-rat16</t>
+          <t>https://www.freepressjournal.in/entertainment/homebound-review-neeraj-ghaywans-film-hits-hard-with-ishaan-khatter-vishal-jethwas-career-defining-performances</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/vhp-issues-hindus-only-diktat-for-garba-events-congress-slams-move/</t>
+          <t>https://www.freepressjournal.in/entertainment/nishaanchi-review-anurag-kashyaps-film-is-full-on-desi-but-very-long-actors-take-the-movie-a-notch-higher</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/chhagan-bhujbal-question-to-sharad-pawar-over-obc-and-maratha-reservation-meeting-maharashtra-news-mhs25091803691</t>
+          <t>https://www.freepressjournal.in/entertainment/the-trial-season-2-review-kajols-series-is-about-pyaar-kanoon-dhokha-and-a-few-loose-ends-tied-up</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/girish-mahajan-comment-on-maratha-reservation-issue-warns-manoj-jarange-patil-sd67</t>
+          <t>https://www.freepressjournal.in/entertainment/mohanlal-wins-dadasaheb-phalke-award-malayalam-actors-daughter-vismaya-pens-heartfelt-note-says-were-all-proud-of-you</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/news/obc-funding-shortfall-chhagan-bhujbal-marathi-news/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-politics-mumbai-vartapatra-social-divide-in-the-state-cabinet/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/aurangabad/obc-reservation-protesters-shout-slogans-during-cm-devendra-fadnavis-speech-chaos-at-hyderabad-mukti-sangram-day/articleshow/123934745.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhujbal-presents-fake-documents-asks-for-committee-to-scrutinise-kunbi-certificates/articleshow/123927743.cms</t>
+          <t>https://chandablast.com/?p=50509</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!videos/vanjari-samaj-leader-balasaheb-sanap-demends-reservation-for-vanjari-in-st-as-per-hyderabad-gazette-watch-video-mhs25091903949</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://english.bombaysamachar.com/mumbai/vhp-stirs-controversy-with-advisory-for-hindu-only-garba-events-in-maharashtra/</t>
+          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-infra-sub-committee-6-members-cm-dy-cms-cabinet-status-10253886/</t>
+          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cabinet-upgrades-infrastructure-sub-committee-to-full-fledged-cabinet-panel-enhancing-decision-making-power</t>
+          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.5dariyanews.com/news/467620-Maharashtra-Govt-Signs-Landmark-MoU-to-Transform-Koradi-into-Eco-Tourism-Hub</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chhagan-bhujbal-devendra-fadnavis-nashik-kumbh-mela-meeting-preparations-politics-gs97</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrapur-jiwati-taluka-deforestation-credit-war-between-bjp-congress-mla-css-98-5372937/</t>
+          <t>https://www.lokmat.com/nagpur/five-pilgrimage-sites-in-nagpur-district-get-b-class-status-a-a382-c719/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://clarionindia.net/shiv-sena-fears-rigging-tampering-with-voter-list-in-maharashtra-local-polls/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/cleanliness-campaign-launched-in-the-state-on-the-occasion-of-prime-minister-narendra-modis-birthday-thousands.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/pune/7500-students-take-cleanliness-pledge-in-pune-to-mark-pm-modis-75th-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/anti-social-element-will-be-arrested-soon-cm-on-vandalism-of-meenatai-thackerays-statue-in-mumbai/articleshow/123955024.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/govt-issued-gr-based-on-hyderabad-gazette-to-resolve-conflict-but-it-backfired-pawar/articleshow/123955159.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/nagpur/five-pilgrimage-sites-in-nagpur-district-get-b-class-status-a-a382-c719/</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>https://www.newsgram.com/politics/2025/09/18/ssubt-fears-rigging-tampering-with-voter-list-in-maha</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
           <t>https://www.freepressjournal.in/pune/videos-long-queues-outside-kopa-mall-in-punes-koregaon-park-as-iphone-17-series-goes-on-sale-in-india</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>https://theprint.in/india/ajit-pawar-downplays-row-with-female-ips-officer/2745526/</t>
         </is>
       </c>
     </row>
